--- a/research/traditional_assets/database/data/colombia/colombia_food_processing.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_food_processing.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08812079161482897</v>
+        <v>0.08784161884417709</v>
       </c>
       <c r="C2">
-        <v>9210.670841529261</v>
+        <v>9174.990546578516</v>
       </c>
       <c r="D2">
-        <v>8998.070841529261</v>
+        <v>9057.821546578516</v>
       </c>
       <c r="E2">
-        <v>-1334.2</v>
+        <v>-1238.769</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>95.43100000000001</v>
       </c>
       <c r="G2">
         <v>212.6</v>
@@ -1451,28 +1451,28 @@
         <v>496.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.8001793</v>
       </c>
       <c r="N2">
-        <v>496.2</v>
+        <v>491.3998207</v>
       </c>
       <c r="O2">
-        <v>173.67</v>
+        <v>171.989937245</v>
       </c>
       <c r="P2">
-        <v>322.53</v>
+        <v>319.409883455</v>
       </c>
       <c r="Q2">
-        <v>432.33</v>
+        <v>429.209883455</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08812079161482897</v>
+        <v>0.08839865539815867</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.619862340926174</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.3711386572581</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08784161884417709</v>
+        <v>0.08756244607352516</v>
       </c>
       <c r="C3">
-        <v>9174.990546578516</v>
+        <v>9140.10909228226</v>
       </c>
       <c r="D3">
-        <v>9057.821546578516</v>
+        <v>9118.371092282259</v>
       </c>
       <c r="E3">
-        <v>-1238.769</v>
+        <v>-1143.338</v>
       </c>
       <c r="F3">
-        <v>95.43100000000001</v>
+        <v>190.862</v>
       </c>
       <c r="G3">
         <v>212.6</v>
@@ -1533,28 +1533,28 @@
         <v>496.2</v>
       </c>
       <c r="M3">
-        <v>4.8001793</v>
+        <v>9.6003586</v>
       </c>
       <c r="N3">
-        <v>491.3998207</v>
+        <v>486.5996414000001</v>
       </c>
       <c r="O3">
-        <v>171.989937245</v>
+        <v>170.30987449</v>
       </c>
       <c r="P3">
-        <v>319.409883455</v>
+        <v>316.28976691</v>
       </c>
       <c r="Q3">
-        <v>429.209883455</v>
+        <v>426.08976691</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08839865539815867</v>
+        <v>0.08868218987094405</v>
       </c>
       <c r="T3">
-        <v>0.619862340926174</v>
+        <v>0.6239881129814492</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.3711386572581</v>
+        <v>51.68556932862904</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08756244607352516</v>
+        <v>0.08728327330287326</v>
       </c>
       <c r="C4">
-        <v>9140.10909228226</v>
+        <v>9106.042606675301</v>
       </c>
       <c r="D4">
-        <v>9118.371092282259</v>
+        <v>9179.7356066753</v>
       </c>
       <c r="E4">
-        <v>-1143.338</v>
+        <v>-1047.907</v>
       </c>
       <c r="F4">
-        <v>190.862</v>
+        <v>286.293</v>
       </c>
       <c r="G4">
         <v>212.6</v>
@@ -1615,28 +1615,28 @@
         <v>496.2</v>
       </c>
       <c r="M4">
-        <v>9.6003586</v>
+        <v>14.4005379</v>
       </c>
       <c r="N4">
-        <v>486.5996414000001</v>
+        <v>481.7994621</v>
       </c>
       <c r="O4">
-        <v>170.30987449</v>
+        <v>168.629811735</v>
       </c>
       <c r="P4">
-        <v>316.28976691</v>
+        <v>313.1696503650001</v>
       </c>
       <c r="Q4">
-        <v>426.08976691</v>
+        <v>422.969650365</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08868218987094405</v>
+        <v>0.08897157041533325</v>
       </c>
       <c r="T4">
-        <v>0.6239881129814492</v>
+        <v>0.6281989525017815</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.68556932862904</v>
+        <v>34.45704621908602</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08728327330287326</v>
+        <v>0.08700410053222135</v>
       </c>
       <c r="C5">
-        <v>9106.042606675301</v>
+        <v>9072.807654885684</v>
       </c>
       <c r="D5">
-        <v>9179.7356066753</v>
+        <v>9241.931654885684</v>
       </c>
       <c r="E5">
-        <v>-1047.907</v>
+        <v>-952.4760000000002</v>
       </c>
       <c r="F5">
-        <v>286.293</v>
+        <v>381.724</v>
       </c>
       <c r="G5">
         <v>212.6</v>
@@ -1697,28 +1697,28 @@
         <v>496.2</v>
       </c>
       <c r="M5">
-        <v>14.4005379</v>
+        <v>19.2007172</v>
       </c>
       <c r="N5">
-        <v>481.7994621</v>
+        <v>476.9992828000001</v>
       </c>
       <c r="O5">
-        <v>168.629811735</v>
+        <v>166.94974898</v>
       </c>
       <c r="P5">
-        <v>313.1696503650001</v>
+        <v>310.0495338200001</v>
       </c>
       <c r="Q5">
-        <v>422.969650365</v>
+        <v>419.84953382</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08897157041533325</v>
+        <v>0.08926697972106391</v>
       </c>
       <c r="T5">
-        <v>0.6281989525017815</v>
+        <v>0.6324975178454543</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.45704621908602</v>
+        <v>25.84278466431452</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08700410053222135</v>
+        <v>0.08672492776156947</v>
       </c>
       <c r="C6">
-        <v>9072.807654885684</v>
+        <v>9040.421254042989</v>
       </c>
       <c r="D6">
-        <v>9241.931654885684</v>
+        <v>9304.976254042989</v>
       </c>
       <c r="E6">
-        <v>-952.4760000000002</v>
+        <v>-857.0450000000003</v>
       </c>
       <c r="F6">
-        <v>381.724</v>
+        <v>477.155</v>
       </c>
       <c r="G6">
         <v>212.6</v>
@@ -1779,28 +1779,28 @@
         <v>496.2</v>
       </c>
       <c r="M6">
-        <v>19.2007172</v>
+        <v>24.0008965</v>
       </c>
       <c r="N6">
-        <v>476.9992828000001</v>
+        <v>472.1991035</v>
       </c>
       <c r="O6">
-        <v>166.94974898</v>
+        <v>165.269686225</v>
       </c>
       <c r="P6">
-        <v>310.0495338200001</v>
+        <v>306.929417275</v>
       </c>
       <c r="Q6">
-        <v>419.84953382</v>
+        <v>416.7294172749999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08926697972106391</v>
+        <v>0.08956860817007312</v>
       </c>
       <c r="T6">
-        <v>0.6324975178454543</v>
+        <v>0.6368865793016254</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.84278466431452</v>
+        <v>20.67422773145162</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08672492776156947</v>
+        <v>0.08644575499091754</v>
       </c>
       <c r="C7">
-        <v>9040.421254042989</v>
+        <v>9008.900888801087</v>
       </c>
       <c r="D7">
-        <v>9304.976254042989</v>
+        <v>9368.886888801086</v>
       </c>
       <c r="E7">
-        <v>-857.0450000000003</v>
+        <v>-761.6140000000003</v>
       </c>
       <c r="F7">
-        <v>477.155</v>
+        <v>572.586</v>
       </c>
       <c r="G7">
         <v>212.6</v>
@@ -1861,28 +1861,28 @@
         <v>496.2</v>
       </c>
       <c r="M7">
-        <v>24.0008965</v>
+        <v>28.8010758</v>
       </c>
       <c r="N7">
-        <v>472.1991035</v>
+        <v>467.3989242000001</v>
       </c>
       <c r="O7">
-        <v>165.269686225</v>
+        <v>163.58962347</v>
       </c>
       <c r="P7">
-        <v>306.929417275</v>
+        <v>303.80930073</v>
       </c>
       <c r="Q7">
-        <v>416.7294172749999</v>
+        <v>413.60930073</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08956860817007312</v>
+        <v>0.08987665424565697</v>
       </c>
       <c r="T7">
-        <v>0.6368865793016254</v>
+        <v>0.641369025044098</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.67422773145162</v>
+        <v>17.22852310954302</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08644575499091754</v>
+        <v>0.08616658222026566</v>
       </c>
       <c r="C8">
-        <v>9008.900888801087</v>
+        <v>8978.264527504918</v>
       </c>
       <c r="D8">
-        <v>9368.886888801086</v>
+        <v>9433.681527504918</v>
       </c>
       <c r="E8">
-        <v>-761.6140000000003</v>
+        <v>-666.1830000000003</v>
       </c>
       <c r="F8">
-        <v>572.586</v>
+        <v>668.0169999999999</v>
       </c>
       <c r="G8">
         <v>212.6</v>
@@ -1943,28 +1943,28 @@
         <v>496.2</v>
       </c>
       <c r="M8">
-        <v>28.8010758</v>
+        <v>33.6012551</v>
       </c>
       <c r="N8">
-        <v>467.3989242000001</v>
+        <v>462.5987449</v>
       </c>
       <c r="O8">
-        <v>163.58962347</v>
+        <v>161.909560715</v>
       </c>
       <c r="P8">
-        <v>303.80930073</v>
+        <v>300.689184185</v>
       </c>
       <c r="Q8">
-        <v>413.60930073</v>
+        <v>410.489184185</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08987665424565697</v>
+        <v>0.09019132496802758</v>
       </c>
       <c r="T8">
-        <v>0.641369025044098</v>
+        <v>0.6459478674692043</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.22852310954302</v>
+        <v>14.76730552246544</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08616658222026564</v>
+        <v>0.08588740944961375</v>
       </c>
       <c r="C9">
-        <v>8978.264527504922</v>
+        <v>8948.530639032953</v>
       </c>
       <c r="D9">
-        <v>9433.681527504921</v>
+        <v>9499.378639032953</v>
       </c>
       <c r="E9">
-        <v>-666.1830000000002</v>
+        <v>-570.7520000000002</v>
       </c>
       <c r="F9">
-        <v>668.0170000000001</v>
+        <v>763.4480000000001</v>
       </c>
       <c r="G9">
         <v>212.6</v>
@@ -2025,28 +2025,28 @@
         <v>496.2</v>
       </c>
       <c r="M9">
-        <v>33.6012551</v>
+        <v>38.4014344</v>
       </c>
       <c r="N9">
-        <v>462.5987449</v>
+        <v>457.7985656000001</v>
       </c>
       <c r="O9">
-        <v>161.909560715</v>
+        <v>160.22949796</v>
       </c>
       <c r="P9">
-        <v>300.689184185</v>
+        <v>297.5690676400001</v>
       </c>
       <c r="Q9">
-        <v>410.489184185</v>
+        <v>407.36906764</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09019132496802758</v>
+        <v>0.09051283635827581</v>
       </c>
       <c r="T9">
-        <v>0.6459478674692043</v>
+        <v>0.6506262499470304</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.76730552246544</v>
+        <v>12.92139233215726</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08588740944961375</v>
+        <v>0.08560823667896185</v>
       </c>
       <c r="C10">
-        <v>8948.530639032953</v>
+        <v>8919.718210348166</v>
       </c>
       <c r="D10">
-        <v>9499.378639032953</v>
+        <v>9565.997210348167</v>
       </c>
       <c r="E10">
-        <v>-570.7520000000002</v>
+        <v>-475.3210000000003</v>
       </c>
       <c r="F10">
-        <v>763.4480000000001</v>
+        <v>858.879</v>
       </c>
       <c r="G10">
         <v>212.6</v>
@@ -2107,28 +2107,28 @@
         <v>496.2</v>
       </c>
       <c r="M10">
-        <v>38.4014344</v>
+        <v>43.2016137</v>
       </c>
       <c r="N10">
-        <v>457.7985656000001</v>
+        <v>452.9983863</v>
       </c>
       <c r="O10">
-        <v>160.22949796</v>
+        <v>158.549435205</v>
       </c>
       <c r="P10">
-        <v>297.5690676400001</v>
+        <v>294.448951095</v>
       </c>
       <c r="Q10">
-        <v>407.36906764</v>
+        <v>404.248951095</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09051283635827581</v>
+        <v>0.09084141393292511</v>
       </c>
       <c r="T10">
-        <v>0.6506262499470304</v>
+        <v>0.6554074540177759</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.92139233215726</v>
+        <v>11.48568207302868</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08560823667896185</v>
+        <v>0.08532906390830995</v>
       </c>
       <c r="C11">
-        <v>8919.718210348166</v>
+        <v>8891.846764792861</v>
       </c>
       <c r="D11">
-        <v>9565.997210348167</v>
+        <v>9633.55676479286</v>
       </c>
       <c r="E11">
-        <v>-475.3210000000003</v>
+        <v>-379.8900000000003</v>
       </c>
       <c r="F11">
-        <v>858.879</v>
+        <v>954.3099999999999</v>
       </c>
       <c r="G11">
         <v>212.6</v>
@@ -2189,28 +2189,28 @@
         <v>496.2</v>
       </c>
       <c r="M11">
-        <v>43.2016137</v>
+        <v>48.00179299999999</v>
       </c>
       <c r="N11">
-        <v>452.9983863</v>
+        <v>448.198207</v>
       </c>
       <c r="O11">
-        <v>158.549435205</v>
+        <v>156.86937245</v>
       </c>
       <c r="P11">
-        <v>294.448951095</v>
+        <v>291.32883455</v>
       </c>
       <c r="Q11">
-        <v>404.248951095</v>
+        <v>401.12883455</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09084141393292511</v>
+        <v>0.0911772932314555</v>
       </c>
       <c r="T11">
-        <v>0.6554074540177759</v>
+        <v>0.6602949070678711</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.48568207302868</v>
+        <v>10.33711386572581</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08532906390830995</v>
+        <v>0.08504989113765805</v>
       </c>
       <c r="C12">
-        <v>8891.846764792861</v>
+        <v>8864.93638116418</v>
       </c>
       <c r="D12">
-        <v>9633.55676479286</v>
+        <v>9702.077381164179</v>
       </c>
       <c r="E12">
-        <v>-379.8900000000002</v>
+        <v>-284.4590000000003</v>
       </c>
       <c r="F12">
-        <v>954.3100000000001</v>
+        <v>1049.741</v>
       </c>
       <c r="G12">
         <v>212.6</v>
@@ -2271,28 +2271,28 @@
         <v>496.2</v>
       </c>
       <c r="M12">
-        <v>48.001793</v>
+        <v>52.8019723</v>
       </c>
       <c r="N12">
-        <v>448.198207</v>
+        <v>443.3980277000001</v>
       </c>
       <c r="O12">
-        <v>156.86937245</v>
+        <v>155.189309695</v>
       </c>
       <c r="P12">
-        <v>291.32883455</v>
+        <v>288.208718005</v>
       </c>
       <c r="Q12">
-        <v>401.12883455</v>
+        <v>398.008718005</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0911772932314555</v>
+        <v>0.09152072037939107</v>
       </c>
       <c r="T12">
-        <v>0.6602949070678711</v>
+        <v>0.6652921905235866</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.33711386572581</v>
+        <v>9.397376241568917</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08504989113765805</v>
+        <v>0.08488771836700615</v>
       </c>
       <c r="C13">
-        <v>8864.93638116418</v>
+        <v>8809.758760888453</v>
       </c>
       <c r="D13">
-        <v>9702.077381164179</v>
+        <v>9742.330760888453</v>
       </c>
       <c r="E13">
-        <v>-284.4590000000003</v>
+        <v>-189.0280000000002</v>
       </c>
       <c r="F13">
-        <v>1049.741</v>
+        <v>1145.172</v>
       </c>
       <c r="G13">
         <v>212.6</v>
@@ -2353,45 +2353,45 @@
         <v>496.2</v>
       </c>
       <c r="M13">
-        <v>52.8019723</v>
+        <v>59.3199096</v>
       </c>
       <c r="N13">
-        <v>443.3980277000001</v>
+        <v>436.8800904</v>
       </c>
       <c r="O13">
-        <v>155.189309695</v>
+        <v>152.90803164</v>
       </c>
       <c r="P13">
-        <v>288.208718005</v>
+        <v>283.97205876</v>
       </c>
       <c r="Q13">
-        <v>398.008718005</v>
+        <v>393.77205876</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09152072037939107</v>
+        <v>0.09187195268977971</v>
       </c>
       <c r="T13">
-        <v>0.6652921905235866</v>
+        <v>0.6704030486032955</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.397376241568917</v>
+        <v>8.364813826351483</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08488771836700615</v>
+        <v>0.08461829559635424</v>
       </c>
       <c r="C14">
-        <v>8809.758760888453</v>
+        <v>8781.945509320776</v>
       </c>
       <c r="D14">
-        <v>9742.330760888453</v>
+        <v>9809.948509320777</v>
       </c>
       <c r="E14">
-        <v>-189.0280000000002</v>
+        <v>-93.59700000000021</v>
       </c>
       <c r="F14">
-        <v>1145.172</v>
+        <v>1240.603</v>
       </c>
       <c r="G14">
         <v>212.6</v>
@@ -2435,28 +2435,28 @@
         <v>496.2</v>
       </c>
       <c r="M14">
-        <v>59.3199096</v>
+        <v>64.2632354</v>
       </c>
       <c r="N14">
-        <v>436.8800904</v>
+        <v>431.9367646000001</v>
       </c>
       <c r="O14">
-        <v>152.90803164</v>
+        <v>151.17786761</v>
       </c>
       <c r="P14">
-        <v>283.97205876</v>
+        <v>280.75889699</v>
       </c>
       <c r="Q14">
-        <v>393.77205876</v>
+        <v>390.55889699</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09187195268977971</v>
+        <v>0.09223125930615431</v>
       </c>
       <c r="T14">
-        <v>0.6704030486032955</v>
+        <v>0.6756313976733425</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.364813826351483</v>
+        <v>7.721366608939831</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08461829559635424</v>
+        <v>0.08434887282570236</v>
       </c>
       <c r="C15">
-        <v>8781.945509320776</v>
+        <v>8755.077435123663</v>
       </c>
       <c r="D15">
-        <v>9809.948509320777</v>
+        <v>9878.511435123663</v>
       </c>
       <c r="E15">
-        <v>-93.59700000000021</v>
+        <v>1.833999999999833</v>
       </c>
       <c r="F15">
-        <v>1240.603</v>
+        <v>1336.034</v>
       </c>
       <c r="G15">
         <v>212.6</v>
@@ -2517,28 +2517,28 @@
         <v>496.2</v>
       </c>
       <c r="M15">
-        <v>64.2632354</v>
+        <v>69.20656120000001</v>
       </c>
       <c r="N15">
-        <v>431.9367646000001</v>
+        <v>426.9934388</v>
       </c>
       <c r="O15">
-        <v>151.17786761</v>
+        <v>149.44770358</v>
       </c>
       <c r="P15">
-        <v>280.75889699</v>
+        <v>277.54573522</v>
       </c>
       <c r="Q15">
-        <v>390.55889699</v>
+        <v>387.34573522</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09223125930615431</v>
+        <v>0.09259892189035157</v>
       </c>
       <c r="T15">
-        <v>0.6756313976733425</v>
+        <v>0.6809813362566465</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.721366608939831</v>
+        <v>7.169840422586984</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08434887282570236</v>
+        <v>0.08424520005505044</v>
       </c>
       <c r="C16">
-        <v>8755.077435123663</v>
+        <v>8686.285200143209</v>
       </c>
       <c r="D16">
-        <v>9878.511435123663</v>
+        <v>9905.150200143209</v>
       </c>
       <c r="E16">
-        <v>1.833999999999833</v>
+        <v>97.2650000000001</v>
       </c>
       <c r="F16">
-        <v>1336.034</v>
+        <v>1431.465</v>
       </c>
       <c r="G16">
         <v>212.6</v>
@@ -2599,45 +2599,45 @@
         <v>496.2</v>
       </c>
       <c r="M16">
-        <v>69.20656120000001</v>
+        <v>76.58337750000001</v>
       </c>
       <c r="N16">
-        <v>426.9934388</v>
+        <v>419.6166225000001</v>
       </c>
       <c r="O16">
-        <v>149.44770358</v>
+        <v>146.865817875</v>
       </c>
       <c r="P16">
-        <v>277.54573522</v>
+        <v>272.7508046250001</v>
       </c>
       <c r="Q16">
-        <v>387.34573522</v>
+        <v>382.550804625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09259892189035157</v>
+        <v>0.09297523535888287</v>
       </c>
       <c r="T16">
-        <v>0.6809813362566465</v>
+        <v>0.6864571557477929</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.169840422586984</v>
+        <v>6.479212803065521</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08424520005505044</v>
+        <v>0.08398682728439855</v>
       </c>
       <c r="C17">
-        <v>8686.285200143209</v>
+        <v>8657.872627253537</v>
       </c>
       <c r="D17">
-        <v>9905.150200143209</v>
+        <v>9972.168627253537</v>
       </c>
       <c r="E17">
-        <v>97.26499999999965</v>
+        <v>192.6959999999999</v>
       </c>
       <c r="F17">
-        <v>1431.465</v>
+        <v>1526.896</v>
       </c>
       <c r="G17">
         <v>212.6</v>
@@ -2681,28 +2681,28 @@
         <v>496.2</v>
       </c>
       <c r="M17">
-        <v>76.5833775</v>
+        <v>81.68893600000001</v>
       </c>
       <c r="N17">
-        <v>419.6166225000001</v>
+        <v>414.511064</v>
       </c>
       <c r="O17">
-        <v>146.865817875</v>
+        <v>145.0788724</v>
       </c>
       <c r="P17">
-        <v>272.7508046250001</v>
+        <v>269.4321916</v>
       </c>
       <c r="Q17">
-        <v>382.550804625</v>
+        <v>379.2321916</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09297523535888287</v>
+        <v>0.09336050867190303</v>
       </c>
       <c r="T17">
-        <v>0.6864571557477929</v>
+        <v>0.6920633518934904</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.479212803065523</v>
+        <v>6.074262002873926</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08398682728439855</v>
+        <v>0.08372845451374664</v>
       </c>
       <c r="C18">
-        <v>8657.872627253537</v>
+        <v>8630.373128040043</v>
       </c>
       <c r="D18">
-        <v>9972.168627253537</v>
+        <v>10040.10012804004</v>
       </c>
       <c r="E18">
-        <v>192.6959999999999</v>
+        <v>288.127</v>
       </c>
       <c r="F18">
-        <v>1526.896</v>
+        <v>1622.327</v>
       </c>
       <c r="G18">
         <v>212.6</v>
@@ -2763,28 +2763,28 @@
         <v>496.2</v>
       </c>
       <c r="M18">
-        <v>81.68893600000001</v>
+        <v>86.79449450000001</v>
       </c>
       <c r="N18">
-        <v>414.511064</v>
+        <v>409.4055055</v>
       </c>
       <c r="O18">
-        <v>145.0788724</v>
+        <v>143.291926925</v>
       </c>
       <c r="P18">
-        <v>269.4321916</v>
+        <v>266.113578575</v>
       </c>
       <c r="Q18">
-        <v>379.2321916</v>
+        <v>375.913578575</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09336050867190303</v>
+        <v>0.09375506567921282</v>
       </c>
       <c r="T18">
-        <v>0.6920633518934904</v>
+        <v>0.6978046371029397</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.074262002873926</v>
+        <v>5.716952473293107</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08372845451374664</v>
+        <v>0.08356368174309473</v>
       </c>
       <c r="C19">
-        <v>8630.373128040043</v>
+        <v>8578.749697624338</v>
       </c>
       <c r="D19">
-        <v>10040.10012804004</v>
+        <v>10083.90769762434</v>
       </c>
       <c r="E19">
-        <v>288.127</v>
+        <v>383.558</v>
       </c>
       <c r="F19">
-        <v>1622.327</v>
+        <v>1717.758</v>
       </c>
       <c r="G19">
         <v>212.6</v>
@@ -2845,45 +2845,45 @@
         <v>496.2</v>
       </c>
       <c r="M19">
-        <v>86.79449450000001</v>
+        <v>93.27425940000002</v>
       </c>
       <c r="N19">
-        <v>409.4055055</v>
+        <v>402.9257406</v>
       </c>
       <c r="O19">
-        <v>143.291926925</v>
+        <v>141.02400921</v>
       </c>
       <c r="P19">
-        <v>266.113578575</v>
+        <v>261.90173139</v>
       </c>
       <c r="Q19">
-        <v>375.913578575</v>
+        <v>371.70173139</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09375506567921282</v>
+        <v>0.09415924602816431</v>
       </c>
       <c r="T19">
-        <v>0.6978046371029397</v>
+        <v>0.7036859536589608</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.716952473293107</v>
+        <v>5.319795656292286</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08356368174309474</v>
+        <v>0.08331050897244284</v>
       </c>
       <c r="C20">
-        <v>8578.749697624335</v>
+        <v>8551.378847186184</v>
       </c>
       <c r="D20">
-        <v>10083.90769762433</v>
+        <v>10151.96784718618</v>
       </c>
       <c r="E20">
-        <v>383.5579999999998</v>
+        <v>478.9889999999998</v>
       </c>
       <c r="F20">
-        <v>1717.758</v>
+        <v>1813.189</v>
       </c>
       <c r="G20">
         <v>212.6</v>
@@ -2927,28 +2927,28 @@
         <v>496.2</v>
       </c>
       <c r="M20">
-        <v>93.27425940000001</v>
+        <v>98.45616270000001</v>
       </c>
       <c r="N20">
-        <v>402.9257406</v>
+        <v>397.7438373000001</v>
       </c>
       <c r="O20">
-        <v>141.02400921</v>
+        <v>139.210343055</v>
       </c>
       <c r="P20">
-        <v>261.90173139</v>
+        <v>258.533494245</v>
       </c>
       <c r="Q20">
-        <v>371.70173139</v>
+        <v>368.333494245</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09415924602816431</v>
+        <v>0.09457340613881832</v>
       </c>
       <c r="T20">
-        <v>0.7036859536589608</v>
+        <v>0.7097124879077233</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.319795656292287</v>
+        <v>5.039806411224272</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08331050897244284</v>
+        <v>0.08305733620179094</v>
       </c>
       <c r="C21">
-        <v>8551.378847186184</v>
+        <v>8524.932967687568</v>
       </c>
       <c r="D21">
-        <v>10151.96784718618</v>
+        <v>10220.95296768757</v>
       </c>
       <c r="E21">
-        <v>478.9889999999998</v>
+        <v>574.4199999999998</v>
       </c>
       <c r="F21">
-        <v>1813.189</v>
+        <v>1908.62</v>
       </c>
       <c r="G21">
         <v>212.6</v>
@@ -3009,28 +3009,28 @@
         <v>496.2</v>
       </c>
       <c r="M21">
-        <v>98.45616270000001</v>
+        <v>103.638066</v>
       </c>
       <c r="N21">
-        <v>397.7438373000001</v>
+        <v>392.5619340000001</v>
       </c>
       <c r="O21">
-        <v>139.210343055</v>
+        <v>137.3966769</v>
       </c>
       <c r="P21">
-        <v>258.533494245</v>
+        <v>255.1652571</v>
       </c>
       <c r="Q21">
-        <v>368.333494245</v>
+        <v>364.9652571</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09457340613881832</v>
+        <v>0.09499792025223867</v>
       </c>
       <c r="T21">
-        <v>0.7097124879077233</v>
+        <v>0.7158896855127049</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.039806411224272</v>
+        <v>4.787816090663059</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08305733620179094</v>
+        <v>0.08280416343113904</v>
       </c>
       <c r="C22">
-        <v>8524.932967687568</v>
+        <v>8499.43104435343</v>
       </c>
       <c r="D22">
-        <v>10220.95296768757</v>
+        <v>10290.88204435343</v>
       </c>
       <c r="E22">
-        <v>574.4199999999998</v>
+        <v>669.8509999999999</v>
       </c>
       <c r="F22">
-        <v>1908.62</v>
+        <v>2004.051</v>
       </c>
       <c r="G22">
         <v>212.6</v>
@@ -3091,28 +3091,28 @@
         <v>496.2</v>
       </c>
       <c r="M22">
-        <v>103.638066</v>
+        <v>108.8199693</v>
       </c>
       <c r="N22">
-        <v>392.5619340000001</v>
+        <v>387.3800307</v>
       </c>
       <c r="O22">
-        <v>137.3966769</v>
+        <v>135.583010745</v>
       </c>
       <c r="P22">
-        <v>255.1652571</v>
+        <v>251.797019955</v>
       </c>
       <c r="Q22">
-        <v>364.9652571</v>
+        <v>361.597019955</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09499792025223867</v>
+        <v>0.09543318155840384</v>
       </c>
       <c r="T22">
-        <v>0.7158896855127049</v>
+        <v>0.7222232678671796</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.787816090663059</v>
+        <v>4.559824848250532</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08280416343113904</v>
+        <v>0.08255099066048714</v>
       </c>
       <c r="C23">
-        <v>8499.43104435343</v>
+        <v>8474.892585555646</v>
       </c>
       <c r="D23">
-        <v>10290.88204435343</v>
+        <v>10361.77458555565</v>
       </c>
       <c r="E23">
-        <v>669.8509999999997</v>
+        <v>765.2819999999997</v>
       </c>
       <c r="F23">
-        <v>2004.051</v>
+        <v>2099.482</v>
       </c>
       <c r="G23">
         <v>212.6</v>
@@ -3173,28 +3173,28 @@
         <v>496.2</v>
       </c>
       <c r="M23">
-        <v>108.8199693</v>
+        <v>114.0018726</v>
       </c>
       <c r="N23">
-        <v>387.3800307</v>
+        <v>382.1981274</v>
       </c>
       <c r="O23">
-        <v>135.583010745</v>
+        <v>133.76934459</v>
       </c>
       <c r="P23">
-        <v>251.797019955</v>
+        <v>248.42878281</v>
       </c>
       <c r="Q23">
-        <v>361.597019955</v>
+        <v>358.22878281</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09543318155840384</v>
+        <v>0.09587960341088093</v>
       </c>
       <c r="T23">
-        <v>0.7222232678671796</v>
+        <v>0.7287192497692049</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.559824848250532</v>
+        <v>4.352560082420962</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08255099066048714</v>
+        <v>0.08244731788983524</v>
       </c>
       <c r="C24">
-        <v>8474.892585555646</v>
+        <v>8408.774341359065</v>
       </c>
       <c r="D24">
-        <v>10361.77458555565</v>
+        <v>10391.08734135907</v>
       </c>
       <c r="E24">
-        <v>765.2819999999997</v>
+        <v>860.7129999999997</v>
       </c>
       <c r="F24">
-        <v>2099.482</v>
+        <v>2194.913</v>
       </c>
       <c r="G24">
         <v>212.6</v>
@@ -3255,45 +3255,45 @@
         <v>496.2</v>
       </c>
       <c r="M24">
-        <v>114.0018726</v>
+        <v>121.3786889</v>
       </c>
       <c r="N24">
-        <v>382.1981274</v>
+        <v>374.8213111000001</v>
       </c>
       <c r="O24">
-        <v>133.76934459</v>
+        <v>131.187458885</v>
       </c>
       <c r="P24">
-        <v>248.42878281</v>
+        <v>243.633852215</v>
       </c>
       <c r="Q24">
-        <v>358.22878281</v>
+        <v>353.433852215</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09587960341088093</v>
+        <v>0.09633762063614965</v>
       </c>
       <c r="T24">
-        <v>0.7287192497692049</v>
+        <v>0.7353839584738803</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.352560082420962</v>
+        <v>4.088032293781022</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08244731788983524</v>
+        <v>0.08220064511918333</v>
       </c>
       <c r="C25">
-        <v>8408.774341359065</v>
+        <v>8383.759629207441</v>
       </c>
       <c r="D25">
-        <v>10391.08734135907</v>
+        <v>10461.50362920744</v>
       </c>
       <c r="E25">
-        <v>860.7129999999997</v>
+        <v>956.1439999999998</v>
       </c>
       <c r="F25">
-        <v>2194.913</v>
+        <v>2290.344</v>
       </c>
       <c r="G25">
         <v>212.6</v>
@@ -3337,28 +3337,28 @@
         <v>496.2</v>
       </c>
       <c r="M25">
-        <v>121.3786889</v>
+        <v>126.6560232</v>
       </c>
       <c r="N25">
-        <v>374.8213111000001</v>
+        <v>369.5439768000001</v>
       </c>
       <c r="O25">
-        <v>131.187458885</v>
+        <v>129.34039188</v>
       </c>
       <c r="P25">
-        <v>243.633852215</v>
+        <v>240.2035849200001</v>
       </c>
       <c r="Q25">
-        <v>353.433852215</v>
+        <v>350.00358492</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09633762063614965</v>
+        <v>0.09680769094629385</v>
       </c>
       <c r="T25">
-        <v>0.7353839584738803</v>
+        <v>0.7422240542497314</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.088032293781022</v>
+        <v>3.917697614873479</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08220064511918333</v>
+        <v>0.08195397234853144</v>
       </c>
       <c r="C26">
-        <v>8383.759629207441</v>
+        <v>8359.70579519419</v>
       </c>
       <c r="D26">
-        <v>10461.50362920744</v>
+        <v>10532.88079519419</v>
       </c>
       <c r="E26">
-        <v>956.1439999999998</v>
+        <v>1051.575</v>
       </c>
       <c r="F26">
-        <v>2290.344</v>
+        <v>2385.775</v>
       </c>
       <c r="G26">
         <v>212.6</v>
@@ -3419,28 +3419,28 @@
         <v>496.2</v>
       </c>
       <c r="M26">
-        <v>126.6560232</v>
+        <v>131.9333575</v>
       </c>
       <c r="N26">
-        <v>369.5439768000001</v>
+        <v>364.2666425</v>
       </c>
       <c r="O26">
-        <v>129.34039188</v>
+        <v>127.493324875</v>
       </c>
       <c r="P26">
-        <v>240.2035849200001</v>
+        <v>236.773317625</v>
       </c>
       <c r="Q26">
-        <v>350.00358492</v>
+        <v>346.573317625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09680769094629385</v>
+        <v>0.09729029646470858</v>
       </c>
       <c r="T26">
-        <v>0.7422240542497314</v>
+        <v>0.7492465525796052</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.917697614873479</v>
+        <v>3.76098971027854</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08195397234853144</v>
+        <v>0.08170729957787953</v>
       </c>
       <c r="C27">
-        <v>8359.70579519419</v>
+        <v>8336.632642184652</v>
       </c>
       <c r="D27">
-        <v>10532.88079519419</v>
+        <v>10605.23864218465</v>
       </c>
       <c r="E27">
-        <v>1051.575</v>
+        <v>1147.006</v>
       </c>
       <c r="F27">
-        <v>2385.775</v>
+        <v>2481.206</v>
       </c>
       <c r="G27">
         <v>212.6</v>
@@ -3501,28 +3501,28 @@
         <v>496.2</v>
       </c>
       <c r="M27">
-        <v>131.9333575</v>
+        <v>137.2106918</v>
       </c>
       <c r="N27">
-        <v>364.2666425</v>
+        <v>358.9893082</v>
       </c>
       <c r="O27">
-        <v>127.493324875</v>
+        <v>125.64625787</v>
       </c>
       <c r="P27">
-        <v>236.773317625</v>
+        <v>233.34305033</v>
       </c>
       <c r="Q27">
-        <v>346.573317625</v>
+        <v>343.14305033</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09729029646470858</v>
+        <v>0.09778594537551288</v>
       </c>
       <c r="T27">
-        <v>0.7492465525796052</v>
+        <v>0.7564588481616376</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.76098971027854</v>
+        <v>3.616336259883211</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08170729957787953</v>
+        <v>0.08146062680722763</v>
       </c>
       <c r="C28">
-        <v>8336.632642184652</v>
+        <v>8314.560520968074</v>
       </c>
       <c r="D28">
-        <v>10605.23864218465</v>
+        <v>10678.59752096807</v>
       </c>
       <c r="E28">
-        <v>1147.006</v>
+        <v>1242.437</v>
       </c>
       <c r="F28">
-        <v>2481.206</v>
+        <v>2576.637</v>
       </c>
       <c r="G28">
         <v>212.6</v>
@@ -3583,28 +3583,28 @@
         <v>496.2</v>
       </c>
       <c r="M28">
-        <v>137.2106918</v>
+        <v>142.4880261</v>
       </c>
       <c r="N28">
-        <v>358.9893082</v>
+        <v>353.7119739</v>
       </c>
       <c r="O28">
-        <v>125.64625787</v>
+        <v>123.799190865</v>
       </c>
       <c r="P28">
-        <v>233.34305033</v>
+        <v>229.912783035</v>
       </c>
       <c r="Q28">
-        <v>343.14305033</v>
+        <v>339.712783035</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09778594537551288</v>
+        <v>0.098295173708531</v>
       </c>
       <c r="T28">
-        <v>0.7564588481616376</v>
+        <v>0.7638687408829038</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.616336259883211</v>
+        <v>3.482397879887537</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08146062680722763</v>
+        <v>0.08121395403657572</v>
       </c>
       <c r="C29">
-        <v>8314.560520968074</v>
+        <v>8293.510349340224</v>
       </c>
       <c r="D29">
-        <v>10678.59752096807</v>
+        <v>10752.97834934022</v>
       </c>
       <c r="E29">
-        <v>1242.437</v>
+        <v>1337.868</v>
       </c>
       <c r="F29">
-        <v>2576.637</v>
+        <v>2672.068</v>
       </c>
       <c r="G29">
         <v>212.6</v>
@@ -3665,28 +3665,28 @@
         <v>496.2</v>
       </c>
       <c r="M29">
-        <v>142.4880261</v>
+        <v>147.7653604</v>
       </c>
       <c r="N29">
-        <v>353.7119739</v>
+        <v>348.4346396</v>
       </c>
       <c r="O29">
-        <v>123.799190865</v>
+        <v>121.95212386</v>
       </c>
       <c r="P29">
-        <v>229.912783035</v>
+        <v>226.48251574</v>
       </c>
       <c r="Q29">
-        <v>339.712783035</v>
+        <v>336.28251574</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.098295173708531</v>
+        <v>0.09881854727302183</v>
       </c>
       <c r="T29">
-        <v>0.7638687408829038</v>
+        <v>0.7714844639575386</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.482397879887537</v>
+        <v>3.35802652703441</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08121395403657572</v>
+        <v>0.08096728126592383</v>
       </c>
       <c r="C30">
-        <v>8293.510349340224</v>
+        <v>8273.503631989044</v>
       </c>
       <c r="D30">
-        <v>10752.97834934022</v>
+        <v>10828.40263198904</v>
       </c>
       <c r="E30">
-        <v>1337.868</v>
+        <v>1433.299</v>
       </c>
       <c r="F30">
-        <v>2672.068</v>
+        <v>2767.499</v>
       </c>
       <c r="G30">
         <v>212.6</v>
@@ -3747,28 +3747,28 @@
         <v>496.2</v>
       </c>
       <c r="M30">
-        <v>147.7653604</v>
+        <v>153.0426947</v>
       </c>
       <c r="N30">
-        <v>348.4346396</v>
+        <v>343.1573053</v>
       </c>
       <c r="O30">
-        <v>121.95212386</v>
+        <v>120.105056855</v>
       </c>
       <c r="P30">
-        <v>226.48251574</v>
+        <v>223.052248445</v>
       </c>
       <c r="Q30">
-        <v>336.28251574</v>
+        <v>332.852248445</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09881854727302183</v>
+        <v>0.09935666375482229</v>
       </c>
       <c r="T30">
-        <v>0.7714844639575386</v>
+        <v>0.7793147144427264</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.35802652703441</v>
+        <v>3.24223250886081</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08096728126592383</v>
+        <v>0.08072060849527192</v>
       </c>
       <c r="C31">
-        <v>8273.503631989044</v>
+        <v>8254.562481223165</v>
       </c>
       <c r="D31">
-        <v>10828.40263198904</v>
+        <v>10904.89248122317</v>
       </c>
       <c r="E31">
-        <v>1433.299</v>
+        <v>1528.73</v>
       </c>
       <c r="F31">
-        <v>2767.499</v>
+        <v>2862.93</v>
       </c>
       <c r="G31">
         <v>212.6</v>
@@ -3829,28 +3829,28 @@
         <v>496.2</v>
       </c>
       <c r="M31">
-        <v>153.0426947</v>
+        <v>158.320029</v>
       </c>
       <c r="N31">
-        <v>343.1573053000001</v>
+        <v>337.8799710000001</v>
       </c>
       <c r="O31">
-        <v>120.105056855</v>
+        <v>118.25798985</v>
       </c>
       <c r="P31">
-        <v>223.0522484450001</v>
+        <v>219.6219811500001</v>
       </c>
       <c r="Q31">
-        <v>332.852248445</v>
+        <v>329.42198115</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09935666375482229</v>
+        <v>0.0999101549932456</v>
       </c>
       <c r="T31">
-        <v>0.7793147144427264</v>
+        <v>0.7873686863703481</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.24223250886081</v>
+        <v>3.134158091898783</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08072060849527192</v>
+        <v>0.08047393572462001</v>
       </c>
       <c r="C32">
-        <v>8254.562481223165</v>
+        <v>8236.709638585169</v>
       </c>
       <c r="D32">
-        <v>10904.89248122317</v>
+        <v>10982.47063858517</v>
       </c>
       <c r="E32">
-        <v>1528.73</v>
+        <v>1624.161</v>
       </c>
       <c r="F32">
-        <v>2862.93</v>
+        <v>2958.361</v>
       </c>
       <c r="G32">
         <v>212.6</v>
@@ -3911,28 +3911,28 @@
         <v>496.2</v>
       </c>
       <c r="M32">
-        <v>158.320029</v>
+        <v>163.5973633</v>
       </c>
       <c r="N32">
-        <v>337.8799710000001</v>
+        <v>332.6026367000001</v>
       </c>
       <c r="O32">
-        <v>118.25798985</v>
+        <v>116.410922845</v>
       </c>
       <c r="P32">
-        <v>219.6219811500001</v>
+        <v>216.191713855</v>
       </c>
       <c r="Q32">
-        <v>329.42198115</v>
+        <v>325.991713855</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0999101549932456</v>
+        <v>0.100479689455971</v>
       </c>
       <c r="T32">
-        <v>0.7873686863703481</v>
+        <v>0.7956561067596402</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.134158091898783</v>
+        <v>3.033056217966565</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08047393572462001</v>
+        <v>0.08074726295396813</v>
       </c>
       <c r="C33">
-        <v>8236.709638585169</v>
+        <v>8055.383263173496</v>
       </c>
       <c r="D33">
-        <v>10982.47063858517</v>
+        <v>10896.5752631735</v>
       </c>
       <c r="E33">
-        <v>1624.161</v>
+        <v>1719.592</v>
       </c>
       <c r="F33">
-        <v>2958.361</v>
+        <v>3053.792</v>
       </c>
       <c r="G33">
         <v>212.6</v>
@@ -3993,45 +3993,45 @@
         <v>496.2</v>
       </c>
       <c r="M33">
-        <v>163.5973633</v>
+        <v>176.5091776</v>
       </c>
       <c r="N33">
-        <v>332.6026367000001</v>
+        <v>319.6908224</v>
       </c>
       <c r="O33">
-        <v>116.410922845</v>
+        <v>111.89178784</v>
       </c>
       <c r="P33">
-        <v>216.191713855</v>
+        <v>207.79903456</v>
       </c>
       <c r="Q33">
-        <v>325.991713855</v>
+        <v>317.59903456</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.100479689455971</v>
+        <v>0.1010659749323061</v>
       </c>
       <c r="T33">
-        <v>0.7956561067596402</v>
+        <v>0.8041872748074408</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.033056217966565</v>
+        <v>2.811185269496151</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08074726295396813</v>
+        <v>0.0805168401833162</v>
       </c>
       <c r="C34">
-        <v>8055.383263173496</v>
+        <v>8032.275062411551</v>
       </c>
       <c r="D34">
-        <v>10896.5752631735</v>
+        <v>10968.89806241155</v>
       </c>
       <c r="E34">
-        <v>1719.592</v>
+        <v>1815.023</v>
       </c>
       <c r="F34">
-        <v>3053.792</v>
+        <v>3149.223</v>
       </c>
       <c r="G34">
         <v>212.6</v>
@@ -4075,28 +4075,28 @@
         <v>496.2</v>
       </c>
       <c r="M34">
-        <v>176.5091776</v>
+        <v>182.0250894</v>
       </c>
       <c r="N34">
-        <v>319.6908224</v>
+        <v>314.1749106</v>
       </c>
       <c r="O34">
-        <v>111.89178784</v>
+        <v>109.96121871</v>
       </c>
       <c r="P34">
-        <v>207.79903456</v>
+        <v>204.21369189</v>
       </c>
       <c r="Q34">
-        <v>317.59903456</v>
+        <v>314.01369189</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1010659749323061</v>
+        <v>0.1016697614676361</v>
       </c>
       <c r="T34">
-        <v>0.8041872748074408</v>
+        <v>0.8129731045880114</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.811185269496151</v>
+        <v>2.725997837087176</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0805168401833162</v>
+        <v>0.08028641741266432</v>
       </c>
       <c r="C35">
-        <v>8032.275062411551</v>
+        <v>8010.133318651047</v>
       </c>
       <c r="D35">
-        <v>10968.89806241155</v>
+        <v>11042.18731865105</v>
       </c>
       <c r="E35">
-        <v>1815.023</v>
+        <v>1910.454</v>
       </c>
       <c r="F35">
-        <v>3149.223</v>
+        <v>3244.654</v>
       </c>
       <c r="G35">
         <v>212.6</v>
@@ -4157,28 +4157,28 @@
         <v>496.2</v>
       </c>
       <c r="M35">
-        <v>182.0250894</v>
+        <v>187.5410012</v>
       </c>
       <c r="N35">
-        <v>314.1749106</v>
+        <v>308.6589988</v>
       </c>
       <c r="O35">
-        <v>109.96121871</v>
+        <v>108.03064958</v>
       </c>
       <c r="P35">
-        <v>204.21369189</v>
+        <v>200.62834922</v>
       </c>
       <c r="Q35">
-        <v>314.01369189</v>
+        <v>310.42834922</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1016697614676361</v>
+        <v>0.1022918445646429</v>
       </c>
       <c r="T35">
-        <v>0.8129731045880114</v>
+        <v>0.8220251716346602</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.725997837087176</v>
+        <v>2.645821430114024</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08028641741266432</v>
+        <v>0.08005599464201242</v>
       </c>
       <c r="C36">
-        <v>8010.133318651047</v>
+        <v>7988.977534496053</v>
       </c>
       <c r="D36">
-        <v>11042.18731865105</v>
+        <v>11116.46253449605</v>
       </c>
       <c r="E36">
-        <v>1910.454</v>
+        <v>2005.885</v>
       </c>
       <c r="F36">
-        <v>3244.654</v>
+        <v>3340.085</v>
       </c>
       <c r="G36">
         <v>212.6</v>
@@ -4239,28 +4239,28 @@
         <v>496.2</v>
       </c>
       <c r="M36">
-        <v>187.5410012</v>
+        <v>193.056913</v>
       </c>
       <c r="N36">
-        <v>308.6589988</v>
+        <v>303.143087</v>
       </c>
       <c r="O36">
-        <v>108.03064958</v>
+        <v>106.10008045</v>
       </c>
       <c r="P36">
-        <v>200.62834922</v>
+        <v>197.04300655</v>
       </c>
       <c r="Q36">
-        <v>310.42834922</v>
+        <v>306.84300655</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1022918445646429</v>
+        <v>0.1029330686800191</v>
       </c>
       <c r="T36">
-        <v>0.8220251716346602</v>
+        <v>0.8313557638212057</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.645821430114024</v>
+        <v>2.570226532110767</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08005599464201242</v>
+        <v>0.08064457187136051</v>
       </c>
       <c r="C37">
-        <v>7988.977534496053</v>
+        <v>7705.772761787331</v>
       </c>
       <c r="D37">
-        <v>11116.46253449605</v>
+        <v>10928.68876178733</v>
       </c>
       <c r="E37">
-        <v>2005.885</v>
+        <v>2101.316</v>
       </c>
       <c r="F37">
-        <v>3340.085</v>
+        <v>3435.516000000001</v>
       </c>
       <c r="G37">
         <v>212.6</v>
@@ -4321,45 +4321,45 @@
         <v>496.2</v>
       </c>
       <c r="M37">
-        <v>193.056913</v>
+        <v>210.5971308</v>
       </c>
       <c r="N37">
-        <v>303.143087</v>
+        <v>285.6028692</v>
       </c>
       <c r="O37">
-        <v>106.10008045</v>
+        <v>99.96100421999999</v>
       </c>
       <c r="P37">
-        <v>197.04300655</v>
+        <v>185.64186498</v>
       </c>
       <c r="Q37">
-        <v>306.84300655</v>
+        <v>295.4418649799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1029330686800191</v>
+        <v>0.1035943310490008</v>
       </c>
       <c r="T37">
-        <v>0.8313557638212057</v>
+        <v>0.8409779370135807</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.570226532110767</v>
+        <v>2.356157456253435</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08064457187136052</v>
+        <v>0.08043689910070861</v>
       </c>
       <c r="C38">
-        <v>7705.772761787328</v>
+        <v>7675.867000295366</v>
       </c>
       <c r="D38">
-        <v>10928.68876178733</v>
+        <v>10994.21400029537</v>
       </c>
       <c r="E38">
-        <v>2101.316</v>
+        <v>2196.747</v>
       </c>
       <c r="F38">
-        <v>3435.516</v>
+        <v>3530.947</v>
       </c>
       <c r="G38">
         <v>212.6</v>
@@ -4403,28 +4403,28 @@
         <v>496.2</v>
       </c>
       <c r="M38">
-        <v>210.5971308</v>
+        <v>216.4470511</v>
       </c>
       <c r="N38">
-        <v>285.6028692</v>
+        <v>279.7529489</v>
       </c>
       <c r="O38">
-        <v>99.96100422000001</v>
+        <v>97.91353211500001</v>
       </c>
       <c r="P38">
-        <v>185.64186498</v>
+        <v>181.839416785</v>
       </c>
       <c r="Q38">
-        <v>295.44186498</v>
+        <v>291.639416785</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1035943310490008</v>
+        <v>0.1042765858741407</v>
       </c>
       <c r="T38">
-        <v>0.8409779370135807</v>
+        <v>0.8509055760215867</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.356157456253436</v>
+        <v>2.292477525003343</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08043689910070861</v>
+        <v>0.08092082633005672</v>
       </c>
       <c r="C39">
-        <v>7675.867000295366</v>
+        <v>7428.947550962672</v>
       </c>
       <c r="D39">
-        <v>10994.21400029537</v>
+        <v>10842.72555096267</v>
       </c>
       <c r="E39">
-        <v>2196.747</v>
+        <v>2292.178</v>
       </c>
       <c r="F39">
-        <v>3530.947</v>
+        <v>3626.378</v>
       </c>
       <c r="G39">
         <v>212.6</v>
@@ -4485,45 +4485,45 @@
         <v>496.2</v>
       </c>
       <c r="M39">
-        <v>216.4470511</v>
+        <v>232.4508298</v>
       </c>
       <c r="N39">
-        <v>279.7529489</v>
+        <v>263.7491702</v>
       </c>
       <c r="O39">
-        <v>97.91353211500001</v>
+        <v>92.31220956999999</v>
       </c>
       <c r="P39">
-        <v>181.839416785</v>
+        <v>171.43696063</v>
       </c>
       <c r="Q39">
-        <v>291.639416785</v>
+        <v>281.2369606299999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1042765858741407</v>
+        <v>0.1049808489194463</v>
       </c>
       <c r="T39">
-        <v>0.8509055760215867</v>
+        <v>0.8611534614492058</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.292477525003343</v>
+        <v>2.134644993209656</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08092082633005672</v>
+        <v>0.08073135355940483</v>
       </c>
       <c r="C40">
-        <v>7428.947550962672</v>
+        <v>7392.329080172717</v>
       </c>
       <c r="D40">
-        <v>10842.72555096267</v>
+        <v>10901.53808017272</v>
       </c>
       <c r="E40">
-        <v>2292.178</v>
+        <v>2387.609</v>
       </c>
       <c r="F40">
-        <v>3626.378</v>
+        <v>3721.809</v>
       </c>
       <c r="G40">
         <v>212.6</v>
@@ -4567,28 +4567,28 @@
         <v>496.2</v>
       </c>
       <c r="M40">
-        <v>232.4508298</v>
+        <v>238.5679569</v>
       </c>
       <c r="N40">
-        <v>263.7491702</v>
+        <v>257.6320431</v>
       </c>
       <c r="O40">
-        <v>92.31220956999999</v>
+        <v>90.171215085</v>
       </c>
       <c r="P40">
-        <v>171.43696063</v>
+        <v>167.460828015</v>
       </c>
       <c r="Q40">
-        <v>281.2369606299999</v>
+        <v>277.260828015</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1049808489194463</v>
+        <v>0.1057082025564013</v>
       </c>
       <c r="T40">
-        <v>0.8611534614492058</v>
+        <v>0.8717373431203536</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.134644993209656</v>
+        <v>2.079910506204281</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08073135355940483</v>
+        <v>0.08054188078875291</v>
       </c>
       <c r="C41">
-        <v>7392.329080172717</v>
+        <v>7356.352104466258</v>
       </c>
       <c r="D41">
-        <v>10901.53808017272</v>
+        <v>10960.99210446626</v>
       </c>
       <c r="E41">
-        <v>2387.609</v>
+        <v>2483.04</v>
       </c>
       <c r="F41">
-        <v>3721.809</v>
+        <v>3817.24</v>
       </c>
       <c r="G41">
         <v>212.6</v>
@@ -4649,28 +4649,28 @@
         <v>496.2</v>
       </c>
       <c r="M41">
-        <v>238.5679569</v>
+        <v>244.685084</v>
       </c>
       <c r="N41">
-        <v>257.6320431</v>
+        <v>251.514916</v>
       </c>
       <c r="O41">
-        <v>90.171215085</v>
+        <v>88.03022060000001</v>
       </c>
       <c r="P41">
-        <v>167.460828015</v>
+        <v>163.4846954</v>
       </c>
       <c r="Q41">
-        <v>277.260828015</v>
+        <v>273.2846954</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1057082025564013</v>
+        <v>0.1064598013145882</v>
       </c>
       <c r="T41">
-        <v>0.8717373431203536</v>
+        <v>0.8826740208472059</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.079910506204281</v>
+        <v>2.027912743549174</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08054188078875291</v>
+        <v>0.08243110801810101</v>
       </c>
       <c r="C42">
-        <v>7356.352104466258</v>
+        <v>6695.614569534402</v>
       </c>
       <c r="D42">
-        <v>10960.99210446626</v>
+        <v>10395.6855695344</v>
       </c>
       <c r="E42">
-        <v>2483.04</v>
+        <v>2578.471</v>
       </c>
       <c r="F42">
-        <v>3817.24</v>
+        <v>3912.671</v>
       </c>
       <c r="G42">
         <v>212.6</v>
@@ -4731,45 +4731,45 @@
         <v>496.2</v>
       </c>
       <c r="M42">
-        <v>244.685084</v>
+        <v>281.3210449000001</v>
       </c>
       <c r="N42">
-        <v>251.514916</v>
+        <v>214.8789551</v>
       </c>
       <c r="O42">
-        <v>88.03022060000001</v>
+        <v>75.20763428499998</v>
       </c>
       <c r="P42">
-        <v>163.4846954</v>
+        <v>139.671320815</v>
       </c>
       <c r="Q42">
-        <v>273.2846954</v>
+        <v>249.471320815</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1064598013145882</v>
+        <v>0.1072368779967814</v>
       </c>
       <c r="T42">
-        <v>0.8826740208472059</v>
+        <v>0.8939814334122569</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.027912743549174</v>
+        <v>1.76382111824013</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08243110801810101</v>
+        <v>0.0833570352474491</v>
       </c>
       <c r="C43">
-        <v>6695.614569534402</v>
+        <v>6343.889421895932</v>
       </c>
       <c r="D43">
-        <v>10395.6855695344</v>
+        <v>10139.39142189593</v>
       </c>
       <c r="E43">
-        <v>2578.471</v>
+        <v>2673.902</v>
       </c>
       <c r="F43">
-        <v>3912.671</v>
+        <v>4008.102</v>
       </c>
       <c r="G43">
         <v>212.6</v>
@@ -4813,45 +4813,45 @@
         <v>496.2</v>
       </c>
       <c r="M43">
-        <v>281.3210449000001</v>
+        <v>303.8141316000001</v>
       </c>
       <c r="N43">
-        <v>214.8789551</v>
+        <v>192.3858684</v>
       </c>
       <c r="O43">
-        <v>75.20763428499998</v>
+        <v>67.33505393999999</v>
       </c>
       <c r="P43">
-        <v>139.671320815</v>
+        <v>125.05081446</v>
       </c>
       <c r="Q43">
-        <v>249.471320815</v>
+        <v>234.85081446</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1072368779967814</v>
+        <v>0.1080407504266364</v>
       </c>
       <c r="T43">
-        <v>0.8939814334122569</v>
+        <v>0.905678756755413</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.76382111824013</v>
+        <v>1.633235417282347</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08335703524744911</v>
+        <v>0.08324361247679722</v>
       </c>
       <c r="C44">
-        <v>6343.889421895929</v>
+        <v>6279.172281796818</v>
       </c>
       <c r="D44">
-        <v>10139.39142189593</v>
+        <v>10170.10528179682</v>
       </c>
       <c r="E44">
-        <v>2673.902</v>
+        <v>2769.333</v>
       </c>
       <c r="F44">
-        <v>4008.102</v>
+        <v>4103.533</v>
       </c>
       <c r="G44">
         <v>212.6</v>
@@ -4895,28 +4895,28 @@
         <v>496.2</v>
       </c>
       <c r="M44">
-        <v>303.8141316</v>
+        <v>311.0478014</v>
       </c>
       <c r="N44">
-        <v>192.3858684</v>
+        <v>185.1521986</v>
       </c>
       <c r="O44">
-        <v>67.33505394000001</v>
+        <v>64.80326951000001</v>
       </c>
       <c r="P44">
-        <v>125.05081446</v>
+        <v>120.34892909</v>
       </c>
       <c r="Q44">
-        <v>234.85081446</v>
+        <v>230.14892909</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1080407504266364</v>
+        <v>0.1088728289066618</v>
       </c>
       <c r="T44">
-        <v>0.905678756755413</v>
+        <v>0.9177865124965747</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.633235417282348</v>
+        <v>1.595253198275781</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08324361247679722</v>
+        <v>0.08313018970614532</v>
       </c>
       <c r="C45">
-        <v>6279.172281796818</v>
+        <v>6214.641781578983</v>
       </c>
       <c r="D45">
-        <v>10170.10528179682</v>
+        <v>10201.00578157898</v>
       </c>
       <c r="E45">
-        <v>2769.333</v>
+        <v>2864.764</v>
       </c>
       <c r="F45">
-        <v>4103.533</v>
+        <v>4198.964</v>
       </c>
       <c r="G45">
         <v>212.6</v>
@@ -4977,28 +4977,28 @@
         <v>496.2</v>
       </c>
       <c r="M45">
-        <v>311.0478014</v>
+        <v>318.2814712</v>
       </c>
       <c r="N45">
-        <v>185.1521986</v>
+        <v>177.9185288</v>
       </c>
       <c r="O45">
-        <v>64.80326951000001</v>
+        <v>62.27148508000001</v>
       </c>
       <c r="P45">
-        <v>120.34892909</v>
+        <v>115.64704372</v>
       </c>
       <c r="Q45">
-        <v>230.14892909</v>
+        <v>225.44704372</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1088728289066618</v>
+        <v>0.1097346244752595</v>
       </c>
       <c r="T45">
-        <v>0.9177865124965747</v>
+        <v>0.9303266880856348</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.595253198275781</v>
+        <v>1.558997443769514</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08313018970614532</v>
+        <v>0.08301676693549341</v>
       </c>
       <c r="C46">
-        <v>6214.641781578983</v>
+        <v>6150.29962766785</v>
       </c>
       <c r="D46">
-        <v>10201.00578157898</v>
+        <v>10232.09462766785</v>
       </c>
       <c r="E46">
-        <v>2864.764</v>
+        <v>2960.195</v>
       </c>
       <c r="F46">
-        <v>4198.964</v>
+        <v>4294.395</v>
       </c>
       <c r="G46">
         <v>212.6</v>
@@ -5059,28 +5059,28 @@
         <v>496.2</v>
       </c>
       <c r="M46">
-        <v>318.2814712</v>
+        <v>325.5151410000001</v>
       </c>
       <c r="N46">
-        <v>177.9185288</v>
+        <v>170.684859</v>
       </c>
       <c r="O46">
-        <v>62.27148508000001</v>
+        <v>59.73970064999998</v>
       </c>
       <c r="P46">
-        <v>115.64704372</v>
+        <v>110.94515835</v>
       </c>
       <c r="Q46">
-        <v>225.44704372</v>
+        <v>220.7451583499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1097346244752595</v>
+        <v>0.1106277580645335</v>
       </c>
       <c r="T46">
-        <v>0.9303266880856348</v>
+        <v>0.9433228700597518</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.558997443769514</v>
+        <v>1.524353056130191</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08301676693549341</v>
+        <v>0.08714914416484151</v>
       </c>
       <c r="C47">
-        <v>6150.29962766785</v>
+        <v>5032.287007130656</v>
       </c>
       <c r="D47">
-        <v>10232.09462766785</v>
+        <v>9209.513007130656</v>
       </c>
       <c r="E47">
-        <v>2960.195</v>
+        <v>3055.626</v>
       </c>
       <c r="F47">
-        <v>4294.395</v>
+        <v>4389.826</v>
       </c>
       <c r="G47">
         <v>212.6</v>
@@ -5141,45 +5141,45 @@
         <v>496.2</v>
       </c>
       <c r="M47">
-        <v>325.5151410000001</v>
+        <v>395.08434</v>
       </c>
       <c r="N47">
-        <v>170.684859</v>
+        <v>101.11566</v>
       </c>
       <c r="O47">
-        <v>59.73970064999998</v>
+        <v>35.39048100000002</v>
       </c>
       <c r="P47">
-        <v>110.94515835</v>
+        <v>65.72517900000003</v>
       </c>
       <c r="Q47">
-        <v>220.7451583499999</v>
+        <v>175.525179</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1106277580645335</v>
+        <v>0.1115539706756324</v>
       </c>
       <c r="T47">
-        <v>0.9433228700597518</v>
+        <v>0.9568003921069843</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.524353056130191</v>
+        <v>1.255934365811614</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08714914416484151</v>
+        <v>0.09764442020053613</v>
       </c>
       <c r="C48">
-        <v>5032.287007130656</v>
+        <v>3072.501448042412</v>
       </c>
       <c r="D48">
-        <v>9209.513007130656</v>
+        <v>7345.158448042412</v>
       </c>
       <c r="E48">
-        <v>3055.626</v>
+        <v>3151.057</v>
       </c>
       <c r="F48">
-        <v>4389.826</v>
+        <v>4485.257000000001</v>
       </c>
       <c r="G48">
         <v>212.6</v>
@@ -5223,45 +5223,45 @@
         <v>496.2</v>
       </c>
       <c r="M48">
-        <v>395.08434</v>
+        <v>531.9514802000001</v>
       </c>
       <c r="N48">
-        <v>101.11566</v>
+        <v>-35.75148020000006</v>
       </c>
       <c r="O48">
-        <v>35.39048100000002</v>
+        <v>-12.51301807000002</v>
       </c>
       <c r="P48">
-        <v>65.72517900000003</v>
+        <v>-23.23846213000004</v>
       </c>
       <c r="Q48">
-        <v>175.525179</v>
+        <v>86.56153786999991</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1115539706756324</v>
+        <v>0.1133979418134838</v>
       </c>
       <c r="T48">
-        <v>0.9568003921069843</v>
+        <v>0.9836324189732183</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V48">
-        <v>0.35</v>
+        <v>0.3264771439957354</v>
       </c>
       <c r="W48">
-        <v>0.0585</v>
+        <v>0.0798798107221058</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.255934365811614</v>
+        <v>0.9327918399878155</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09764442020053613</v>
+        <v>0.09837242020053613</v>
       </c>
       <c r="C49">
-        <v>3072.501448042412</v>
+        <v>2875.357889826947</v>
       </c>
       <c r="D49">
-        <v>7345.158448042412</v>
+        <v>7243.445889826947</v>
       </c>
       <c r="E49">
-        <v>3151.057</v>
+        <v>3246.488</v>
       </c>
       <c r="F49">
-        <v>4485.257000000001</v>
+        <v>4580.688</v>
       </c>
       <c r="G49">
         <v>212.6</v>
@@ -5305,37 +5305,37 @@
         <v>496.2</v>
       </c>
       <c r="M49">
-        <v>531.9514802000001</v>
+        <v>543.2695968</v>
       </c>
       <c r="N49">
-        <v>-35.75148020000006</v>
+        <v>-47.0695968</v>
       </c>
       <c r="O49">
-        <v>-12.51301807000002</v>
+        <v>-16.47435888</v>
       </c>
       <c r="P49">
-        <v>-23.23846213000004</v>
+        <v>-30.59523792</v>
       </c>
       <c r="Q49">
-        <v>86.56153786999991</v>
+        <v>79.20476207999995</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1133979418134838</v>
+        <v>0.1146979022329739</v>
       </c>
       <c r="T49">
-        <v>0.9836324189732183</v>
+        <v>1.002548427030396</v>
       </c>
       <c r="U49">
         <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.3264771439957354</v>
+        <v>0.3196755368291576</v>
       </c>
       <c r="W49">
-        <v>0.0798798107221058</v>
+        <v>0.08068648133206191</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9327918399878155</v>
+        <v>0.913358676654736</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0983724202005361</v>
+        <v>0.09910042020053611</v>
       </c>
       <c r="C50">
-        <v>2875.357889826951</v>
+        <v>2680.992799102071</v>
       </c>
       <c r="D50">
-        <v>7243.44588982695</v>
+        <v>7144.511799102071</v>
       </c>
       <c r="E50">
-        <v>3246.488</v>
+        <v>3341.918999999999</v>
       </c>
       <c r="F50">
-        <v>4580.688</v>
+        <v>4676.119</v>
       </c>
       <c r="G50">
         <v>212.6</v>
@@ -5387,37 +5387,37 @@
         <v>496.2</v>
       </c>
       <c r="M50">
-        <v>543.2695968</v>
+        <v>554.5877134</v>
       </c>
       <c r="N50">
-        <v>-47.0695968</v>
+        <v>-58.38771339999994</v>
       </c>
       <c r="O50">
-        <v>-16.47435888</v>
+        <v>-20.43569968999998</v>
       </c>
       <c r="P50">
-        <v>-30.59523792</v>
+        <v>-37.95201370999996</v>
       </c>
       <c r="Q50">
-        <v>79.20476207999995</v>
+        <v>71.84798628999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1146979022329738</v>
+        <v>0.1160488414924439</v>
       </c>
       <c r="T50">
-        <v>1.002548427030395</v>
+        <v>1.022206239325109</v>
       </c>
       <c r="U50">
         <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.3196755368291576</v>
+        <v>0.3131515462816238</v>
       </c>
       <c r="W50">
-        <v>0.08068648133206191</v>
+        <v>0.08146022661099943</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.913358676654736</v>
+        <v>0.8947187036617823</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09910042020053611</v>
+        <v>0.09982842020053612</v>
       </c>
       <c r="C51">
-        <v>2680.992799102071</v>
+        <v>2489.293861404814</v>
       </c>
       <c r="D51">
-        <v>7144.511799102071</v>
+        <v>7048.243861404814</v>
       </c>
       <c r="E51">
-        <v>3341.918999999999</v>
+        <v>3437.35</v>
       </c>
       <c r="F51">
-        <v>4676.119</v>
+        <v>4771.55</v>
       </c>
       <c r="G51">
         <v>212.6</v>
@@ -5469,37 +5469,37 @@
         <v>496.2</v>
       </c>
       <c r="M51">
-        <v>554.5877134</v>
+        <v>565.90583</v>
       </c>
       <c r="N51">
-        <v>-58.38771339999994</v>
+        <v>-69.70582999999999</v>
       </c>
       <c r="O51">
-        <v>-20.43569968999998</v>
+        <v>-24.3970405</v>
       </c>
       <c r="P51">
-        <v>-37.95201370999996</v>
+        <v>-45.3087895</v>
       </c>
       <c r="Q51">
-        <v>71.84798628999999</v>
+        <v>64.49121049999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1160488414924439</v>
+        <v>0.1174538183222928</v>
       </c>
       <c r="T51">
-        <v>1.022206239325109</v>
+        <v>1.042650364111611</v>
       </c>
       <c r="U51">
         <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.3131515462816238</v>
+        <v>0.3068885153559913</v>
       </c>
       <c r="W51">
-        <v>0.08146022661099943</v>
+        <v>0.08220302207877944</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8947187036617823</v>
+        <v>0.8768243295885466</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09982842020053612</v>
+        <v>0.1005564202005361</v>
       </c>
       <c r="C52">
-        <v>2489.293861404814</v>
+        <v>2300.154735265253</v>
       </c>
       <c r="D52">
-        <v>7048.243861404814</v>
+        <v>6954.535735265254</v>
       </c>
       <c r="E52">
-        <v>3437.35</v>
+        <v>3532.781</v>
       </c>
       <c r="F52">
-        <v>4771.55</v>
+        <v>4866.981000000001</v>
       </c>
       <c r="G52">
         <v>212.6</v>
@@ -5551,37 +5551,37 @@
         <v>496.2</v>
       </c>
       <c r="M52">
-        <v>565.90583</v>
+        <v>577.2239466000001</v>
       </c>
       <c r="N52">
-        <v>-69.70582999999999</v>
+        <v>-81.02394660000004</v>
       </c>
       <c r="O52">
-        <v>-24.3970405</v>
+        <v>-28.35838131000001</v>
       </c>
       <c r="P52">
-        <v>-45.3087895</v>
+        <v>-52.66556529000003</v>
       </c>
       <c r="Q52">
-        <v>64.49121049999997</v>
+        <v>57.13443470999992</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1174538183222928</v>
+        <v>0.1189161411451967</v>
       </c>
       <c r="T52">
-        <v>1.042650364111611</v>
+        <v>1.063928942971032</v>
       </c>
       <c r="U52">
         <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.3068885153559913</v>
+        <v>0.300871093486266</v>
       </c>
       <c r="W52">
-        <v>0.08220302207877944</v>
+        <v>0.08291668831252887</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8768243295885466</v>
+        <v>0.8596316956750456</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1005564202005361</v>
+        <v>0.1012844202005361</v>
       </c>
       <c r="C53">
-        <v>2300.154735265253</v>
+        <v>2113.474660354235</v>
       </c>
       <c r="D53">
-        <v>6954.535735265254</v>
+        <v>6863.286660354235</v>
       </c>
       <c r="E53">
-        <v>3532.781</v>
+        <v>3628.212</v>
       </c>
       <c r="F53">
-        <v>4866.981000000001</v>
+        <v>4962.412</v>
       </c>
       <c r="G53">
         <v>212.6</v>
@@ -5633,37 +5633,37 @@
         <v>496.2</v>
       </c>
       <c r="M53">
-        <v>577.2239466000001</v>
+        <v>588.5420632</v>
       </c>
       <c r="N53">
-        <v>-81.02394660000004</v>
+        <v>-92.34206319999998</v>
       </c>
       <c r="O53">
-        <v>-28.35838131000001</v>
+        <v>-32.31972211999999</v>
       </c>
       <c r="P53">
-        <v>-52.66556529000003</v>
+        <v>-60.02234107999999</v>
       </c>
       <c r="Q53">
-        <v>57.13443470999992</v>
+        <v>49.77765891999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1189161411451967</v>
+        <v>0.1204393940857217</v>
       </c>
       <c r="T53">
-        <v>1.063928942971032</v>
+        <v>1.086094129282928</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.300871093486266</v>
+        <v>0.2950851109192224</v>
       </c>
       <c r="W53">
-        <v>0.08291668831252887</v>
+        <v>0.08360290584498023</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8596316956750456</v>
+        <v>0.843100316912064</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1012844202005361</v>
+        <v>0.1020124202005361</v>
       </c>
       <c r="C54">
-        <v>2113.474660354235</v>
+        <v>1929.158096080128</v>
       </c>
       <c r="D54">
-        <v>6863.286660354235</v>
+        <v>6774.401096080129</v>
       </c>
       <c r="E54">
-        <v>3628.212</v>
+        <v>3723.643</v>
       </c>
       <c r="F54">
-        <v>4962.412</v>
+        <v>5057.843000000001</v>
       </c>
       <c r="G54">
         <v>212.6</v>
@@ -5715,37 +5715,37 @@
         <v>496.2</v>
       </c>
       <c r="M54">
-        <v>588.5420632</v>
+        <v>599.8601798000002</v>
       </c>
       <c r="N54">
-        <v>-92.34206319999998</v>
+        <v>-103.6601798000002</v>
       </c>
       <c r="O54">
-        <v>-32.31972211999999</v>
+        <v>-36.28106293000005</v>
       </c>
       <c r="P54">
-        <v>-60.02234107999999</v>
+        <v>-67.3791168700001</v>
       </c>
       <c r="Q54">
-        <v>49.77765891999996</v>
+        <v>42.42088312999985</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1204393940857217</v>
+        <v>0.1220274663003115</v>
       </c>
       <c r="T54">
-        <v>1.086094129282928</v>
+        <v>1.109202515012353</v>
       </c>
       <c r="U54">
         <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2950851109192224</v>
+        <v>0.2895174673169729</v>
       </c>
       <c r="W54">
-        <v>0.08360290584498023</v>
+        <v>0.08426322837620702</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.843100316912064</v>
+        <v>0.8271927637627796</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1020124202005361</v>
+        <v>0.1027404202005361</v>
       </c>
       <c r="C55">
-        <v>1929.158096080128</v>
+        <v>1747.114387909423</v>
       </c>
       <c r="D55">
-        <v>6774.401096080129</v>
+        <v>6687.788387909423</v>
       </c>
       <c r="E55">
-        <v>3723.643</v>
+        <v>3819.074</v>
       </c>
       <c r="F55">
-        <v>5057.843000000001</v>
+        <v>5153.274</v>
       </c>
       <c r="G55">
         <v>212.6</v>
@@ -5797,37 +5797,37 @@
         <v>496.2</v>
       </c>
       <c r="M55">
-        <v>599.8601798000002</v>
+        <v>611.1782964000001</v>
       </c>
       <c r="N55">
-        <v>-103.6601798000002</v>
+        <v>-114.9782964000001</v>
       </c>
       <c r="O55">
-        <v>-36.28106293000005</v>
+        <v>-40.24240374000003</v>
       </c>
       <c r="P55">
-        <v>-67.3791168700001</v>
+        <v>-74.73589266000006</v>
       </c>
       <c r="Q55">
-        <v>42.42088312999985</v>
+        <v>35.06410733999989</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1220274663003115</v>
+        <v>0.1236845851329269</v>
       </c>
       <c r="T55">
-        <v>1.109202515012353</v>
+        <v>1.133315613164795</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2895174673169729</v>
+        <v>0.2841560327370289</v>
       </c>
       <c r="W55">
-        <v>0.08426322837620702</v>
+        <v>0.08489909451738838</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8271927637627796</v>
+        <v>0.8118743792486541</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1027404202005361</v>
+        <v>0.1513367724798823</v>
       </c>
       <c r="C56">
-        <v>1747.114387909423</v>
+        <v>-1427.832053312923</v>
       </c>
       <c r="D56">
-        <v>6687.788387909423</v>
+        <v>3608.272946687078</v>
       </c>
       <c r="E56">
-        <v>3819.074</v>
+        <v>3914.505000000001</v>
       </c>
       <c r="F56">
-        <v>5153.274</v>
+        <v>5248.705000000001</v>
       </c>
       <c r="G56">
         <v>212.6</v>
@@ -5879,45 +5879,45 @@
         <v>496.2</v>
       </c>
       <c r="M56">
-        <v>611.1782964000001</v>
+        <v>1053.939964</v>
       </c>
       <c r="N56">
-        <v>-114.9782964000001</v>
+        <v>-557.7399640000001</v>
       </c>
       <c r="O56">
-        <v>-40.24240374000003</v>
+        <v>-195.2089874</v>
       </c>
       <c r="P56">
-        <v>-74.73589266000006</v>
+        <v>-362.5309766000001</v>
       </c>
       <c r="Q56">
-        <v>35.06410733999989</v>
+        <v>-252.7309766000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1236845851329269</v>
+        <v>0.1313228032010945</v>
       </c>
       <c r="T56">
-        <v>1.133315613164795</v>
+        <v>1.24446099294229</v>
       </c>
       <c r="U56">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.2841560327370289</v>
+        <v>0.1647816820048015</v>
       </c>
       <c r="W56">
-        <v>0.08489909451738838</v>
+        <v>0.1677118382534359</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8118743792486541</v>
+        <v>0.4708048057280044</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1513367724798823</v>
+        <v>0.1528867724798822</v>
       </c>
       <c r="C57">
-        <v>-1427.832053312923</v>
+        <v>-1575.49007386689</v>
       </c>
       <c r="D57">
-        <v>3608.272946687078</v>
+        <v>3556.04592613311</v>
       </c>
       <c r="E57">
-        <v>3914.505000000001</v>
+        <v>4009.936</v>
       </c>
       <c r="F57">
-        <v>5248.705000000001</v>
+        <v>5344.136</v>
       </c>
       <c r="G57">
         <v>212.6</v>
@@ -5961,37 +5961,37 @@
         <v>496.2</v>
       </c>
       <c r="M57">
-        <v>1053.939964</v>
+        <v>1073.1025088</v>
       </c>
       <c r="N57">
-        <v>-557.7399640000001</v>
+        <v>-576.9025088000001</v>
       </c>
       <c r="O57">
-        <v>-195.2089874</v>
+        <v>-201.91587808</v>
       </c>
       <c r="P57">
-        <v>-362.5309766000001</v>
+        <v>-374.9866307200001</v>
       </c>
       <c r="Q57">
-        <v>-252.7309766000001</v>
+        <v>-265.1866307200001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1313228032010945</v>
+        <v>0.1332665032738467</v>
       </c>
       <c r="T57">
-        <v>1.24446099294229</v>
+        <v>1.272744197327342</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1647816820048015</v>
+        <v>0.1618391519690015</v>
       </c>
       <c r="W57">
-        <v>0.1677118382534359</v>
+        <v>0.1683026982846245</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4708048057280044</v>
+        <v>0.4623975770542901</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1528867724798822</v>
+        <v>0.1544367724798823</v>
       </c>
       <c r="C58">
-        <v>-1575.49007386689</v>
+        <v>-1721.657772497432</v>
       </c>
       <c r="D58">
-        <v>3556.04592613311</v>
+        <v>3505.309227502569</v>
       </c>
       <c r="E58">
-        <v>4009.936</v>
+        <v>4105.367</v>
       </c>
       <c r="F58">
-        <v>5344.136</v>
+        <v>5439.567000000001</v>
       </c>
       <c r="G58">
         <v>212.6</v>
@@ -6043,37 +6043,37 @@
         <v>496.2</v>
       </c>
       <c r="M58">
-        <v>1073.1025088</v>
+        <v>1092.2650536</v>
       </c>
       <c r="N58">
-        <v>-576.9025088000001</v>
+        <v>-596.0650536000003</v>
       </c>
       <c r="O58">
-        <v>-201.91587808</v>
+        <v>-208.6227687600001</v>
       </c>
       <c r="P58">
-        <v>-374.9866307200001</v>
+        <v>-387.4422848400002</v>
       </c>
       <c r="Q58">
-        <v>-265.1866307200001</v>
+        <v>-277.6422848400002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1332665032738467</v>
+        <v>0.1353006080011455</v>
       </c>
       <c r="T58">
-        <v>1.272744197327342</v>
+        <v>1.302342899590769</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1618391519690015</v>
+        <v>0.1589998686011243</v>
       </c>
       <c r="W58">
-        <v>0.1683026982846245</v>
+        <v>0.1688728263848943</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4623975770542901</v>
+        <v>0.454285338860355</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1544367724798823</v>
+        <v>0.1559867724798823</v>
       </c>
       <c r="C59">
-        <v>-1721.657772497432</v>
+        <v>-1866.398042388433</v>
       </c>
       <c r="D59">
-        <v>3505.309227502569</v>
+        <v>3455.999957611568</v>
       </c>
       <c r="E59">
-        <v>4105.367</v>
+        <v>4200.798000000001</v>
       </c>
       <c r="F59">
-        <v>5439.567000000001</v>
+        <v>5534.998000000001</v>
       </c>
       <c r="G59">
         <v>212.6</v>
@@ -6125,37 +6125,37 @@
         <v>496.2</v>
       </c>
       <c r="M59">
-        <v>1092.2650536</v>
+        <v>1111.4275984</v>
       </c>
       <c r="N59">
-        <v>-596.0650536000003</v>
+        <v>-615.2275984</v>
       </c>
       <c r="O59">
-        <v>-208.6227687600001</v>
+        <v>-215.32965944</v>
       </c>
       <c r="P59">
-        <v>-387.4422848400002</v>
+        <v>-399.89793896</v>
       </c>
       <c r="Q59">
-        <v>-277.6422848400002</v>
+        <v>-290.0979389600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1353006080011455</v>
+        <v>0.1374315748583156</v>
       </c>
       <c r="T59">
-        <v>1.302342899590769</v>
+        <v>1.333351063866739</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1589998686011243</v>
+        <v>0.1562584915562773</v>
       </c>
       <c r="W59">
-        <v>0.1688728263848943</v>
+        <v>0.1694232948954995</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.454285338860355</v>
+        <v>0.4464528330179353</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1559867724798822</v>
+        <v>0.1575367724798822</v>
       </c>
       <c r="C60">
-        <v>-1866.398042388431</v>
+        <v>-2009.770286934961</v>
       </c>
       <c r="D60">
-        <v>3455.999957611569</v>
+        <v>3408.058713065039</v>
       </c>
       <c r="E60">
-        <v>4200.797999999999</v>
+        <v>4296.228999999999</v>
       </c>
       <c r="F60">
-        <v>5534.998</v>
+        <v>5630.429</v>
       </c>
       <c r="G60">
         <v>212.6</v>
@@ -6207,37 +6207,37 @@
         <v>496.2</v>
       </c>
       <c r="M60">
-        <v>1111.4275984</v>
+        <v>1130.5901432</v>
       </c>
       <c r="N60">
-        <v>-615.2275983999998</v>
+        <v>-634.3901432</v>
       </c>
       <c r="O60">
-        <v>-215.3296594399999</v>
+        <v>-222.03655012</v>
       </c>
       <c r="P60">
-        <v>-399.8979389599999</v>
+        <v>-412.35359308</v>
       </c>
       <c r="Q60">
-        <v>-290.09793896</v>
+        <v>-302.55359308</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1374315748583156</v>
+        <v>0.1396664913182745</v>
       </c>
       <c r="T60">
-        <v>1.333351063866739</v>
+        <v>1.365871821522025</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1562584915562774</v>
+        <v>0.1536100425468489</v>
       </c>
       <c r="W60">
-        <v>0.1694232948954995</v>
+        <v>0.1699551034565927</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4464528330179354</v>
+        <v>0.4388858358481398</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1575367724798822</v>
+        <v>0.1590867724798823</v>
       </c>
       <c r="C61">
-        <v>-2009.770286934961</v>
+        <v>-2151.830658481307</v>
       </c>
       <c r="D61">
-        <v>3408.058713065039</v>
+        <v>3361.429341518693</v>
       </c>
       <c r="E61">
-        <v>4296.228999999999</v>
+        <v>4391.66</v>
       </c>
       <c r="F61">
-        <v>5630.429</v>
+        <v>5725.86</v>
       </c>
       <c r="G61">
         <v>212.6</v>
@@ -6289,37 +6289,37 @@
         <v>496.2</v>
       </c>
       <c r="M61">
-        <v>1130.5901432</v>
+        <v>1149.752688</v>
       </c>
       <c r="N61">
-        <v>-634.3901432</v>
+        <v>-653.552688</v>
       </c>
       <c r="O61">
-        <v>-222.03655012</v>
+        <v>-228.7434408</v>
       </c>
       <c r="P61">
-        <v>-412.35359308</v>
+        <v>-424.8092472</v>
       </c>
       <c r="Q61">
-        <v>-302.55359308</v>
+        <v>-315.0092472000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1396664913182745</v>
+        <v>0.1420131536012313</v>
       </c>
       <c r="T61">
-        <v>1.365871821522025</v>
+        <v>1.400018617060076</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1536100425468489</v>
+        <v>0.1510498751710681</v>
       </c>
       <c r="W61">
-        <v>0.1699551034565927</v>
+        <v>0.1704691850656495</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4388858358481398</v>
+        <v>0.4315710719173375</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1590867724798823</v>
+        <v>0.1606367724798823</v>
       </c>
       <c r="C62">
-        <v>-2151.830658481307</v>
+        <v>-2292.632277724954</v>
       </c>
       <c r="D62">
-        <v>3361.429341518693</v>
+        <v>3316.058722275046</v>
       </c>
       <c r="E62">
-        <v>4391.66</v>
+        <v>4487.091</v>
       </c>
       <c r="F62">
-        <v>5725.86</v>
+        <v>5821.291</v>
       </c>
       <c r="G62">
         <v>212.6</v>
@@ -6371,37 +6371,37 @@
         <v>496.2</v>
       </c>
       <c r="M62">
-        <v>1149.752688</v>
+        <v>1168.9152328</v>
       </c>
       <c r="N62">
-        <v>-653.552688</v>
+        <v>-672.7152328</v>
       </c>
       <c r="O62">
-        <v>-228.7434408</v>
+        <v>-235.45033148</v>
       </c>
       <c r="P62">
-        <v>-424.8092472</v>
+        <v>-437.26490132</v>
       </c>
       <c r="Q62">
-        <v>-315.0092472000001</v>
+        <v>-327.4649013200001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1420131536012313</v>
+        <v>0.1444801575397245</v>
       </c>
       <c r="T62">
-        <v>1.400018617060076</v>
+        <v>1.435916530318027</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1510498751710681</v>
+        <v>0.1485736477092473</v>
       </c>
       <c r="W62">
-        <v>0.1704691850656495</v>
+        <v>0.1709664115399832</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4315710719173375</v>
+        <v>0.4244961363121352</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1606367724798823</v>
+        <v>0.1621867724798823</v>
       </c>
       <c r="C63">
-        <v>-2292.632277724954</v>
+        <v>-2432.225435588854</v>
       </c>
       <c r="D63">
-        <v>3316.058722275046</v>
+        <v>3271.896564411146</v>
       </c>
       <c r="E63">
-        <v>4487.091</v>
+        <v>4582.521999999999</v>
       </c>
       <c r="F63">
-        <v>5821.291</v>
+        <v>5916.722</v>
       </c>
       <c r="G63">
         <v>212.6</v>
@@ -6453,37 +6453,37 @@
         <v>496.2</v>
       </c>
       <c r="M63">
-        <v>1168.9152328</v>
+        <v>1188.0777776</v>
       </c>
       <c r="N63">
-        <v>-672.7152328</v>
+        <v>-691.8777775999999</v>
       </c>
       <c r="O63">
-        <v>-235.45033148</v>
+        <v>-242.15722216</v>
       </c>
       <c r="P63">
-        <v>-437.26490132</v>
+        <v>-449.72055544</v>
       </c>
       <c r="Q63">
-        <v>-327.4649013200001</v>
+        <v>-339.92055544</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1444801575397245</v>
+        <v>0.1470770037907699</v>
       </c>
       <c r="T63">
-        <v>1.435916530318027</v>
+        <v>1.473703807431659</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1485736477092473</v>
+        <v>0.1461772985526466</v>
       </c>
       <c r="W63">
-        <v>0.1709664115399832</v>
+        <v>0.1714475984506286</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4244961363121352</v>
+        <v>0.4176494244361331</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1621867724798823</v>
+        <v>0.1637367724798823</v>
       </c>
       <c r="C64">
-        <v>-2432.225435588854</v>
+        <v>-2570.657779174905</v>
       </c>
       <c r="D64">
-        <v>3271.896564411146</v>
+        <v>3228.895220825096</v>
       </c>
       <c r="E64">
-        <v>4582.521999999999</v>
+        <v>4677.953</v>
       </c>
       <c r="F64">
-        <v>5916.722</v>
+        <v>6012.153</v>
       </c>
       <c r="G64">
         <v>212.6</v>
@@ -6535,37 +6535,37 @@
         <v>496.2</v>
       </c>
       <c r="M64">
-        <v>1188.0777776</v>
+        <v>1207.2403224</v>
       </c>
       <c r="N64">
-        <v>-691.8777775999999</v>
+        <v>-711.0403224000002</v>
       </c>
       <c r="O64">
-        <v>-242.15722216</v>
+        <v>-248.86411284</v>
       </c>
       <c r="P64">
-        <v>-449.72055544</v>
+        <v>-462.1762095600001</v>
       </c>
       <c r="Q64">
-        <v>-339.92055544</v>
+        <v>-352.3762095600001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1470770037907699</v>
+        <v>0.1498142201094393</v>
       </c>
       <c r="T64">
-        <v>1.473703807431659</v>
+        <v>1.513533640064947</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1461772985526466</v>
+        <v>0.1438570239724458</v>
       </c>
       <c r="W64">
-        <v>0.1714475984506286</v>
+        <v>0.1719135095863329</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4176494244361331</v>
+        <v>0.4110200684927022</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1637367724798823</v>
+        <v>0.1652867724798823</v>
       </c>
       <c r="C65">
-        <v>-2570.657779174905</v>
+        <v>-2707.974483244128</v>
       </c>
       <c r="D65">
-        <v>3228.895220825096</v>
+        <v>3187.009516755872</v>
       </c>
       <c r="E65">
-        <v>4677.953</v>
+        <v>4773.384</v>
       </c>
       <c r="F65">
-        <v>6012.153</v>
+        <v>6107.584000000001</v>
       </c>
       <c r="G65">
         <v>212.6</v>
@@ -6617,37 +6617,37 @@
         <v>496.2</v>
       </c>
       <c r="M65">
-        <v>1207.2403224</v>
+        <v>1226.4028672</v>
       </c>
       <c r="N65">
-        <v>-711.0403224000002</v>
+        <v>-730.2028672000001</v>
       </c>
       <c r="O65">
-        <v>-248.86411284</v>
+        <v>-255.57100352</v>
       </c>
       <c r="P65">
-        <v>-462.1762095600001</v>
+        <v>-474.6318636800001</v>
       </c>
       <c r="Q65">
-        <v>-352.3762095600001</v>
+        <v>-364.8318636800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1498142201094393</v>
+        <v>0.1527035040013682</v>
       </c>
       <c r="T65">
-        <v>1.513533640064947</v>
+        <v>1.555576241177862</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1438570239724458</v>
+        <v>0.1416092579728763</v>
       </c>
       <c r="W65">
-        <v>0.1719135095863329</v>
+        <v>0.1723648609990464</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4110200684927022</v>
+        <v>0.4045978799225038</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1652867724798823</v>
+        <v>0.1668367724798823</v>
       </c>
       <c r="C66">
-        <v>-2707.974483244128</v>
+        <v>-2844.21840852097</v>
       </c>
       <c r="D66">
-        <v>3187.009516755872</v>
+        <v>3146.196591479031</v>
       </c>
       <c r="E66">
-        <v>4773.384</v>
+        <v>4868.815000000001</v>
       </c>
       <c r="F66">
-        <v>6107.584000000001</v>
+        <v>6203.015</v>
       </c>
       <c r="G66">
         <v>212.6</v>
@@ -6699,37 +6699,37 @@
         <v>496.2</v>
       </c>
       <c r="M66">
-        <v>1226.4028672</v>
+        <v>1245.565412</v>
       </c>
       <c r="N66">
-        <v>-730.2028672000001</v>
+        <v>-749.3654120000001</v>
       </c>
       <c r="O66">
-        <v>-255.57100352</v>
+        <v>-262.2778942</v>
       </c>
       <c r="P66">
-        <v>-474.6318636800001</v>
+        <v>-487.0875178000001</v>
       </c>
       <c r="Q66">
-        <v>-364.8318636800001</v>
+        <v>-377.2875178000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1527035040013682</v>
+        <v>0.1557578898299787</v>
       </c>
       <c r="T66">
-        <v>1.555576241177862</v>
+        <v>1.600021276640087</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1416092579728763</v>
+        <v>0.1394306540040628</v>
       </c>
       <c r="W66">
-        <v>0.1723648609990464</v>
+        <v>0.1728023246759842</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4045978799225038</v>
+        <v>0.3983732971544652</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1668367724798823</v>
+        <v>0.1683867724798823</v>
       </c>
       <c r="C67">
-        <v>-2844.21840852097</v>
+        <v>-2979.43024798791</v>
       </c>
       <c r="D67">
-        <v>3146.196591479031</v>
+        <v>3106.415752012091</v>
       </c>
       <c r="E67">
-        <v>4868.815000000001</v>
+        <v>4964.246000000001</v>
       </c>
       <c r="F67">
-        <v>6203.015</v>
+        <v>6298.446000000001</v>
       </c>
       <c r="G67">
         <v>212.6</v>
@@ -6781,37 +6781,37 @@
         <v>496.2</v>
       </c>
       <c r="M67">
-        <v>1245.565412</v>
+        <v>1264.7279568</v>
       </c>
       <c r="N67">
-        <v>-749.3654120000001</v>
+        <v>-768.5279568000001</v>
       </c>
       <c r="O67">
-        <v>-262.2778942</v>
+        <v>-268.98478488</v>
       </c>
       <c r="P67">
-        <v>-487.0875178000001</v>
+        <v>-499.5431719200001</v>
       </c>
       <c r="Q67">
-        <v>-377.2875178000001</v>
+        <v>-389.7431719200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1557578898299787</v>
+        <v>0.1589919454132134</v>
       </c>
       <c r="T67">
-        <v>1.600021276640087</v>
+        <v>1.64708072595303</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1394306540040628</v>
+        <v>0.1373180683373346</v>
       </c>
       <c r="W67">
-        <v>0.1728023246759842</v>
+        <v>0.1732265318778632</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3983732971544652</v>
+        <v>0.3923373381066704</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1683867724798823</v>
+        <v>0.1699367724798823</v>
       </c>
       <c r="C68">
-        <v>-2979.43024798791</v>
+        <v>-3113.648662220055</v>
       </c>
       <c r="D68">
-        <v>3106.415752012091</v>
+        <v>3067.628337779945</v>
       </c>
       <c r="E68">
-        <v>4964.246000000001</v>
+        <v>5059.677</v>
       </c>
       <c r="F68">
-        <v>6298.446000000001</v>
+        <v>6393.877</v>
       </c>
       <c r="G68">
         <v>212.6</v>
@@ -6863,37 +6863,37 @@
         <v>496.2</v>
       </c>
       <c r="M68">
-        <v>1264.7279568</v>
+        <v>1283.8905016</v>
       </c>
       <c r="N68">
-        <v>-768.5279568000001</v>
+        <v>-787.6905016000001</v>
       </c>
       <c r="O68">
-        <v>-268.98478488</v>
+        <v>-275.69167556</v>
       </c>
       <c r="P68">
-        <v>-499.5431719200001</v>
+        <v>-511.99882604</v>
       </c>
       <c r="Q68">
-        <v>-389.7431719200001</v>
+        <v>-402.1988260400001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1589919454132134</v>
+        <v>0.1624220043651289</v>
       </c>
       <c r="T68">
-        <v>1.64708072595303</v>
+        <v>1.696992263103122</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1373180683373346</v>
+        <v>0.1352685449293147</v>
       </c>
       <c r="W68">
-        <v>0.1732265318778632</v>
+        <v>0.1736380761781936</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3923373381066704</v>
+        <v>0.3864815569408991</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1699367724798823</v>
+        <v>0.1714867724798823</v>
       </c>
       <c r="C69">
-        <v>-3113.648662220055</v>
+        <v>-3246.910404705864</v>
       </c>
       <c r="D69">
-        <v>3067.628337779945</v>
+        <v>3029.797595294136</v>
       </c>
       <c r="E69">
-        <v>5059.677</v>
+        <v>5155.108</v>
       </c>
       <c r="F69">
-        <v>6393.877</v>
+        <v>6489.308000000001</v>
       </c>
       <c r="G69">
         <v>212.6</v>
@@ -6945,37 +6945,37 @@
         <v>496.2</v>
       </c>
       <c r="M69">
-        <v>1283.8905016</v>
+        <v>1303.0530464</v>
       </c>
       <c r="N69">
-        <v>-787.6905016000001</v>
+        <v>-806.8530464000003</v>
       </c>
       <c r="O69">
-        <v>-275.69167556</v>
+        <v>-282.3985662400001</v>
       </c>
       <c r="P69">
-        <v>-511.99882604</v>
+        <v>-524.4544801600002</v>
       </c>
       <c r="Q69">
-        <v>-402.1988260400001</v>
+        <v>-414.6544801600003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1624220043651289</v>
+        <v>0.1660664420015392</v>
       </c>
       <c r="T69">
-        <v>1.696992263103122</v>
+        <v>1.750023271325095</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1352685449293147</v>
+        <v>0.1332793016215306</v>
       </c>
       <c r="W69">
-        <v>0.1736380761781936</v>
+        <v>0.1740375162343966</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3864815569408991</v>
+        <v>0.3807980046329447</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1714867724798823</v>
+        <v>0.1730367724798823</v>
       </c>
       <c r="C70">
-        <v>-3246.910404705864</v>
+        <v>-3379.250438007919</v>
       </c>
       <c r="D70">
-        <v>3029.797595294136</v>
+        <v>2992.888561992082</v>
       </c>
       <c r="E70">
-        <v>5155.108</v>
+        <v>5250.539000000001</v>
       </c>
       <c r="F70">
-        <v>6489.308000000001</v>
+        <v>6584.739</v>
       </c>
       <c r="G70">
         <v>212.6</v>
@@ -7027,37 +7027,37 @@
         <v>496.2</v>
       </c>
       <c r="M70">
-        <v>1303.0530464</v>
+        <v>1322.2155912</v>
       </c>
       <c r="N70">
-        <v>-806.8530464000003</v>
+        <v>-826.0155912</v>
       </c>
       <c r="O70">
-        <v>-282.3985662400001</v>
+        <v>-289.10545692</v>
       </c>
       <c r="P70">
-        <v>-524.4544801600002</v>
+        <v>-536.91013428</v>
       </c>
       <c r="Q70">
-        <v>-414.6544801600003</v>
+        <v>-427.11013428</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1660664420015392</v>
+        <v>0.1699460046467502</v>
       </c>
       <c r="T70">
-        <v>1.750023271325095</v>
+        <v>1.806475634916227</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1332793016215306</v>
+        <v>0.1313477175400592</v>
       </c>
       <c r="W70">
-        <v>0.1740375162343966</v>
+        <v>0.1744253783179561</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3807980046329447</v>
+        <v>0.3752791929715977</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1730367724798823</v>
+        <v>0.1745867724798823</v>
       </c>
       <c r="C71">
-        <v>-3379.250438007919</v>
+        <v>-3510.702041535446</v>
       </c>
       <c r="D71">
-        <v>2992.888561992082</v>
+        <v>2956.867958464555</v>
       </c>
       <c r="E71">
-        <v>5250.539000000001</v>
+        <v>5345.970000000001</v>
       </c>
       <c r="F71">
-        <v>6584.739</v>
+        <v>6680.170000000001</v>
       </c>
       <c r="G71">
         <v>212.6</v>
@@ -7109,37 +7109,37 @@
         <v>496.2</v>
       </c>
       <c r="M71">
-        <v>1322.2155912</v>
+        <v>1341.378136</v>
       </c>
       <c r="N71">
-        <v>-826.0155912</v>
+        <v>-845.1781360000002</v>
       </c>
       <c r="O71">
-        <v>-289.10545692</v>
+        <v>-295.8123476000001</v>
       </c>
       <c r="P71">
-        <v>-536.91013428</v>
+        <v>-549.3657884000002</v>
       </c>
       <c r="Q71">
-        <v>-427.11013428</v>
+        <v>-439.5657884000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1699460046467502</v>
+        <v>0.1740842048016418</v>
       </c>
       <c r="T71">
-        <v>1.806475634916227</v>
+        <v>1.866691489413435</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1313477175400592</v>
+        <v>0.1294713215752012</v>
       </c>
       <c r="W71">
-        <v>0.1744253783179561</v>
+        <v>0.1748021586276996</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3752791929715977</v>
+        <v>0.369918061643432</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1745867724798823</v>
+        <v>0.1761367724798823</v>
       </c>
       <c r="C72">
-        <v>-3510.702041535446</v>
+        <v>-3641.296911626886</v>
       </c>
       <c r="D72">
-        <v>2956.867958464555</v>
+        <v>2921.704088373115</v>
       </c>
       <c r="E72">
-        <v>5345.970000000001</v>
+        <v>5441.401</v>
       </c>
       <c r="F72">
-        <v>6680.170000000001</v>
+        <v>6775.601000000001</v>
       </c>
       <c r="G72">
         <v>212.6</v>
@@ -7191,37 +7191,37 @@
         <v>496.2</v>
       </c>
       <c r="M72">
-        <v>1341.378136</v>
+        <v>1360.5406808</v>
       </c>
       <c r="N72">
-        <v>-845.1781360000002</v>
+        <v>-864.3406808000002</v>
       </c>
       <c r="O72">
-        <v>-295.8123476000001</v>
+        <v>-302.51923828</v>
       </c>
       <c r="P72">
-        <v>-549.3657884000002</v>
+        <v>-561.8214425200001</v>
       </c>
       <c r="Q72">
-        <v>-439.5657884000002</v>
+        <v>-452.0214425200002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1740842048016418</v>
+        <v>0.178507798070664</v>
       </c>
       <c r="T72">
-        <v>1.866691489413435</v>
+        <v>1.931060161462175</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1294713215752012</v>
+        <v>0.1276477818347054</v>
       </c>
       <c r="W72">
-        <v>0.1748021586276996</v>
+        <v>0.1751683254075912</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.369918061643432</v>
+        <v>0.3647079480991583</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1761367724798822</v>
+        <v>0.1776867724798823</v>
       </c>
       <c r="C73">
-        <v>-3641.296911626884</v>
+        <v>-3771.065254575125</v>
       </c>
       <c r="D73">
-        <v>2921.704088373116</v>
+        <v>2887.366745424875</v>
       </c>
       <c r="E73">
-        <v>5441.401</v>
+        <v>5536.832</v>
       </c>
       <c r="F73">
-        <v>6775.601</v>
+        <v>6871.032</v>
       </c>
       <c r="G73">
         <v>212.6</v>
@@ -7273,37 +7273,37 @@
         <v>496.2</v>
       </c>
       <c r="M73">
-        <v>1360.5406808</v>
+        <v>1379.7032256</v>
       </c>
       <c r="N73">
-        <v>-864.3406808</v>
+        <v>-883.5032256</v>
       </c>
       <c r="O73">
-        <v>-302.51923828</v>
+        <v>-309.22612896</v>
       </c>
       <c r="P73">
-        <v>-561.82144252</v>
+        <v>-574.27709664</v>
       </c>
       <c r="Q73">
-        <v>-452.0214425200001</v>
+        <v>-464.47709664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1785077980706639</v>
+        <v>0.1832473622874734</v>
       </c>
       <c r="T73">
-        <v>1.931060161462173</v>
+        <v>2.000026595800108</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1276477818347054</v>
+        <v>0.1258748959758901</v>
       </c>
       <c r="W73">
-        <v>0.1751683254075911</v>
+        <v>0.1755243208880413</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3647079480991584</v>
+        <v>0.3596425599311145</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1776867724798823</v>
+        <v>0.1792367724798822</v>
       </c>
       <c r="C74">
-        <v>-3771.065254575125</v>
+        <v>-3900.035873169267</v>
       </c>
       <c r="D74">
-        <v>2887.366745424875</v>
+        <v>2853.827126830733</v>
       </c>
       <c r="E74">
-        <v>5536.832</v>
+        <v>5632.262999999999</v>
       </c>
       <c r="F74">
-        <v>6871.032</v>
+        <v>6966.463</v>
       </c>
       <c r="G74">
         <v>212.6</v>
@@ -7355,37 +7355,37 @@
         <v>496.2</v>
       </c>
       <c r="M74">
-        <v>1379.7032256</v>
+        <v>1398.8657704</v>
       </c>
       <c r="N74">
-        <v>-883.5032256</v>
+        <v>-902.6657703999999</v>
       </c>
       <c r="O74">
-        <v>-309.22612896</v>
+        <v>-315.9330196399999</v>
       </c>
       <c r="P74">
-        <v>-574.27709664</v>
+        <v>-586.73275076</v>
       </c>
       <c r="Q74">
-        <v>-464.47709664</v>
+        <v>-476.9327507600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1832473622874734</v>
+        <v>0.1883380053351575</v>
       </c>
       <c r="T74">
-        <v>2.000026595800108</v>
+        <v>2.074101654903816</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1258748959758901</v>
+        <v>0.1241505823323848</v>
       </c>
       <c r="W74">
-        <v>0.1755243208880413</v>
+        <v>0.1758705630676571</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3596425599311145</v>
+        <v>0.3547159495210993</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1792367724798822</v>
+        <v>0.1807867724798823</v>
       </c>
       <c r="C75">
-        <v>-3900.035873169267</v>
+        <v>-4028.236247274031</v>
       </c>
       <c r="D75">
-        <v>2853.827126830733</v>
+        <v>2821.05775272597</v>
       </c>
       <c r="E75">
-        <v>5632.262999999999</v>
+        <v>5727.694</v>
       </c>
       <c r="F75">
-        <v>6966.463</v>
+        <v>7061.894</v>
       </c>
       <c r="G75">
         <v>212.6</v>
@@ -7437,37 +7437,37 @@
         <v>496.2</v>
       </c>
       <c r="M75">
-        <v>1398.8657704</v>
+        <v>1418.0283152</v>
       </c>
       <c r="N75">
-        <v>-902.6657703999999</v>
+        <v>-921.8283152000001</v>
       </c>
       <c r="O75">
-        <v>-315.9330196399999</v>
+        <v>-322.63991032</v>
       </c>
       <c r="P75">
-        <v>-586.73275076</v>
+        <v>-599.1884048800001</v>
       </c>
       <c r="Q75">
-        <v>-476.9327507600001</v>
+        <v>-489.3884048800002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1883380053351575</v>
+        <v>0.1938202363095867</v>
       </c>
       <c r="T75">
-        <v>2.074101654903816</v>
+        <v>2.153874795477039</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1241505823323848</v>
+        <v>0.1224728717603255</v>
       </c>
       <c r="W75">
-        <v>0.1758705630676571</v>
+        <v>0.1762074473505267</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3547159495210993</v>
+        <v>0.3499224907437871</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1807867724798823</v>
+        <v>0.1823367724798823</v>
       </c>
       <c r="C76">
-        <v>-4028.236247274031</v>
+        <v>-4155.692608920612</v>
       </c>
       <c r="D76">
-        <v>2821.05775272597</v>
+        <v>2789.032391079389</v>
       </c>
       <c r="E76">
-        <v>5727.694</v>
+        <v>5823.125</v>
       </c>
       <c r="F76">
-        <v>7061.894</v>
+        <v>7157.325000000001</v>
       </c>
       <c r="G76">
         <v>212.6</v>
@@ -7519,37 +7519,37 @@
         <v>496.2</v>
       </c>
       <c r="M76">
-        <v>1418.0283152</v>
+        <v>1437.19086</v>
       </c>
       <c r="N76">
-        <v>-921.8283152000001</v>
+        <v>-940.9908600000001</v>
       </c>
       <c r="O76">
-        <v>-322.63991032</v>
+        <v>-329.346801</v>
       </c>
       <c r="P76">
-        <v>-599.1884048800001</v>
+        <v>-611.6440590000001</v>
       </c>
       <c r="Q76">
-        <v>-489.3884048800002</v>
+        <v>-501.8440590000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1938202363095867</v>
+        <v>0.1997410457619702</v>
       </c>
       <c r="T76">
-        <v>2.153874795477039</v>
+        <v>2.240029787296121</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1224728717603255</v>
+        <v>0.1208399001368545</v>
       </c>
       <c r="W76">
-        <v>0.1762074473505267</v>
+        <v>0.1765353480525196</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3499224907437871</v>
+        <v>0.3452568575338699</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1823367724798823</v>
+        <v>0.1838867724798823</v>
       </c>
       <c r="C77">
-        <v>-4155.692608920612</v>
+        <v>-4282.430012340265</v>
       </c>
       <c r="D77">
-        <v>2789.032391079389</v>
+        <v>2757.725987659736</v>
       </c>
       <c r="E77">
-        <v>5823.125</v>
+        <v>5918.556</v>
       </c>
       <c r="F77">
-        <v>7157.325000000001</v>
+        <v>7252.756</v>
       </c>
       <c r="G77">
         <v>212.6</v>
@@ -7601,37 +7601,37 @@
         <v>496.2</v>
       </c>
       <c r="M77">
-        <v>1437.19086</v>
+        <v>1456.3534048</v>
       </c>
       <c r="N77">
-        <v>-940.9908600000001</v>
+        <v>-960.1534048000001</v>
       </c>
       <c r="O77">
-        <v>-329.346801</v>
+        <v>-336.05369168</v>
       </c>
       <c r="P77">
-        <v>-611.6440590000001</v>
+        <v>-624.0997131200002</v>
       </c>
       <c r="Q77">
-        <v>-501.8440590000001</v>
+        <v>-514.2997131200002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1997410457619702</v>
+        <v>0.2061552560020523</v>
       </c>
       <c r="T77">
-        <v>2.240029787296121</v>
+        <v>2.333364361766793</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1208399001368545</v>
+        <v>0.1192499014508432</v>
       </c>
       <c r="W77">
-        <v>0.1765353480525196</v>
+        <v>0.1768546197886707</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3452568575338699</v>
+        <v>0.3407140041452664</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1838867724798823</v>
+        <v>0.1854367724798823</v>
       </c>
       <c r="C78">
-        <v>-4282.430012340265</v>
+        <v>-4408.472399333533</v>
       </c>
       <c r="D78">
-        <v>2757.725987659736</v>
+        <v>2727.114600666468</v>
       </c>
       <c r="E78">
-        <v>5918.556</v>
+        <v>6013.987000000001</v>
       </c>
       <c r="F78">
-        <v>7252.756</v>
+        <v>7348.187000000001</v>
       </c>
       <c r="G78">
         <v>212.6</v>
@@ -7683,37 +7683,37 @@
         <v>496.2</v>
       </c>
       <c r="M78">
-        <v>1456.3534048</v>
+        <v>1475.5159496</v>
       </c>
       <c r="N78">
-        <v>-960.1534048000001</v>
+        <v>-979.3159496000001</v>
       </c>
       <c r="O78">
-        <v>-336.05369168</v>
+        <v>-342.76058236</v>
       </c>
       <c r="P78">
-        <v>-624.0997131200002</v>
+        <v>-636.5553672400001</v>
       </c>
       <c r="Q78">
-        <v>-514.2997131200002</v>
+        <v>-526.7553672400002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2061552560020523</v>
+        <v>0.2131272236543154</v>
       </c>
       <c r="T78">
-        <v>2.333364361766793</v>
+        <v>2.434814986191436</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1192499014508432</v>
+        <v>0.1177012014320011</v>
       </c>
       <c r="W78">
-        <v>0.1768546197886707</v>
+        <v>0.1771655987524542</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3407140041452664</v>
+        <v>0.3362891469485746</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1854367724798823</v>
+        <v>0.1869867724798823</v>
       </c>
       <c r="C79">
-        <v>-4408.472399333533</v>
+        <v>-4533.842660333605</v>
       </c>
       <c r="D79">
-        <v>2727.114600666468</v>
+        <v>2697.175339666395</v>
       </c>
       <c r="E79">
-        <v>6013.987000000001</v>
+        <v>6109.418</v>
       </c>
       <c r="F79">
-        <v>7348.187000000001</v>
+        <v>7443.618</v>
       </c>
       <c r="G79">
         <v>212.6</v>
@@ -7765,37 +7765,37 @@
         <v>496.2</v>
       </c>
       <c r="M79">
-        <v>1475.5159496</v>
+        <v>1494.6784944</v>
       </c>
       <c r="N79">
-        <v>-979.3159496000001</v>
+        <v>-998.4784944</v>
       </c>
       <c r="O79">
-        <v>-342.76058236</v>
+        <v>-349.46747304</v>
       </c>
       <c r="P79">
-        <v>-636.5553672400001</v>
+        <v>-649.0110213600001</v>
       </c>
       <c r="Q79">
-        <v>-526.7553672400002</v>
+        <v>-539.2110213600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2131272236543154</v>
+        <v>0.2207330065476934</v>
       </c>
       <c r="T79">
-        <v>2.434814986191436</v>
+        <v>2.545488394654683</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1177012014320011</v>
+        <v>0.1161922116700524</v>
       </c>
       <c r="W79">
-        <v>0.1771655987524542</v>
+        <v>0.1774686038966535</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3362891469485746</v>
+        <v>0.3319777476287211</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1869867724798823</v>
+        <v>0.1885367724798823</v>
       </c>
       <c r="C80">
-        <v>-4533.842660333605</v>
+        <v>-4658.562691491096</v>
       </c>
       <c r="D80">
-        <v>2697.175339666395</v>
+        <v>2667.886308508905</v>
       </c>
       <c r="E80">
-        <v>6109.418</v>
+        <v>6204.849</v>
       </c>
       <c r="F80">
-        <v>7443.618</v>
+        <v>7539.049000000001</v>
       </c>
       <c r="G80">
         <v>212.6</v>
@@ -7847,37 +7847,37 @@
         <v>496.2</v>
       </c>
       <c r="M80">
-        <v>1494.6784944</v>
+        <v>1513.8410392</v>
       </c>
       <c r="N80">
-        <v>-998.4784944</v>
+        <v>-1017.6410392</v>
       </c>
       <c r="O80">
-        <v>-349.46747304</v>
+        <v>-356.1743637200001</v>
       </c>
       <c r="P80">
-        <v>-649.0110213600001</v>
+        <v>-661.4666754800002</v>
       </c>
       <c r="Q80">
-        <v>-539.2110213600001</v>
+        <v>-551.6666754800002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2207330065476934</v>
+        <v>0.2290631497166312</v>
       </c>
       <c r="T80">
-        <v>2.545488394654683</v>
+        <v>2.666702127733478</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1161922116700524</v>
+        <v>0.114721424180558</v>
       </c>
       <c r="W80">
-        <v>0.1774686038966535</v>
+        <v>0.1777639380245439</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3319777476287211</v>
+        <v>0.3277754976587373</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1885367724798823</v>
+        <v>0.1900867724798823</v>
       </c>
       <c r="C81">
-        <v>-4658.562691491096</v>
+        <v>-4782.653448079423</v>
       </c>
       <c r="D81">
-        <v>2667.886308508905</v>
+        <v>2639.226551920577</v>
       </c>
       <c r="E81">
-        <v>6204.849</v>
+        <v>6300.280000000001</v>
       </c>
       <c r="F81">
-        <v>7539.049000000001</v>
+        <v>7634.48</v>
       </c>
       <c r="G81">
         <v>212.6</v>
@@ -7929,37 +7929,37 @@
         <v>496.2</v>
       </c>
       <c r="M81">
-        <v>1513.8410392</v>
+        <v>1533.003584</v>
       </c>
       <c r="N81">
-        <v>-1017.6410392</v>
+        <v>-1036.803584</v>
       </c>
       <c r="O81">
-        <v>-356.1743637200001</v>
+        <v>-362.8812544</v>
       </c>
       <c r="P81">
-        <v>-661.4666754800002</v>
+        <v>-673.9223296</v>
       </c>
       <c r="Q81">
-        <v>-551.6666754800002</v>
+        <v>-564.1223296000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2290631497166312</v>
+        <v>0.2382263072024628</v>
       </c>
       <c r="T81">
-        <v>2.666702127733478</v>
+        <v>2.800037234120152</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.114721424180558</v>
+        <v>0.1132874063783011</v>
       </c>
       <c r="W81">
-        <v>0.1777639380245439</v>
+        <v>0.1780518887992372</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3277754976587373</v>
+        <v>0.3236783039380031</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1900867724798823</v>
+        <v>0.1916367724798823</v>
       </c>
       <c r="C82">
-        <v>-4782.653448079423</v>
+        <v>-4906.134994494534</v>
       </c>
       <c r="D82">
-        <v>2639.226551920577</v>
+        <v>2611.176005505466</v>
       </c>
       <c r="E82">
-        <v>6300.280000000001</v>
+        <v>6395.711000000001</v>
       </c>
       <c r="F82">
-        <v>7634.48</v>
+        <v>7729.911000000001</v>
       </c>
       <c r="G82">
         <v>212.6</v>
@@ -8011,37 +8011,37 @@
         <v>496.2</v>
       </c>
       <c r="M82">
-        <v>1533.003584</v>
+        <v>1552.1661288</v>
       </c>
       <c r="N82">
-        <v>-1036.803584</v>
+        <v>-1055.9661288</v>
       </c>
       <c r="O82">
-        <v>-362.8812544</v>
+        <v>-369.5881450800001</v>
       </c>
       <c r="P82">
-        <v>-673.9223296</v>
+        <v>-686.3779837200002</v>
       </c>
       <c r="Q82">
-        <v>-564.1223296000001</v>
+        <v>-576.5779837200002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2382263072024628</v>
+        <v>0.2483540075815398</v>
       </c>
       <c r="T82">
-        <v>2.800037234120152</v>
+        <v>2.947407614863319</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1132874063783011</v>
+        <v>0.1118887964230134</v>
       </c>
       <c r="W82">
-        <v>0.1780518887992372</v>
+        <v>0.1783327296782589</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3236783039380031</v>
+        <v>0.3196822754943239</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1916367724798823</v>
+        <v>0.1931867724798823</v>
       </c>
       <c r="C83">
-        <v>-4906.134994494534</v>
+        <v>-5029.02655109968</v>
       </c>
       <c r="D83">
-        <v>2611.176005505466</v>
+        <v>2583.715448900321</v>
       </c>
       <c r="E83">
-        <v>6395.711000000001</v>
+        <v>6491.142</v>
       </c>
       <c r="F83">
-        <v>7729.911000000001</v>
+        <v>7825.342000000001</v>
       </c>
       <c r="G83">
         <v>212.6</v>
@@ -8093,37 +8093,37 @@
         <v>496.2</v>
       </c>
       <c r="M83">
-        <v>1552.1661288</v>
+        <v>1571.3286736</v>
       </c>
       <c r="N83">
-        <v>-1055.9661288</v>
+        <v>-1075.1286736</v>
       </c>
       <c r="O83">
-        <v>-369.5881450800001</v>
+        <v>-376.29503576</v>
       </c>
       <c r="P83">
-        <v>-686.3779837200002</v>
+        <v>-698.8336378400002</v>
       </c>
       <c r="Q83">
-        <v>-576.5779837200002</v>
+        <v>-589.0336378400002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2483540075815398</v>
+        <v>0.2596070080027364</v>
       </c>
       <c r="T83">
-        <v>2.947407614863319</v>
+        <v>3.111152482355725</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1118887964230134</v>
+        <v>0.1105242989056596</v>
       </c>
       <c r="W83">
-        <v>0.1783327296782589</v>
+        <v>0.1786067207797435</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3196822754943239</v>
+        <v>0.3157837111590274</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1931867724798823</v>
+        <v>0.1947367724798823</v>
       </c>
       <c r="C84">
-        <v>-5029.02655109968</v>
+        <v>-5151.346538145081</v>
       </c>
       <c r="D84">
-        <v>2583.715448900321</v>
+        <v>2556.82646185492</v>
       </c>
       <c r="E84">
-        <v>6491.142</v>
+        <v>6586.573</v>
       </c>
       <c r="F84">
-        <v>7825.342000000001</v>
+        <v>7920.773000000001</v>
       </c>
       <c r="G84">
         <v>212.6</v>
@@ -8175,37 +8175,37 @@
         <v>496.2</v>
       </c>
       <c r="M84">
-        <v>1571.3286736</v>
+        <v>1590.4912184</v>
       </c>
       <c r="N84">
-        <v>-1075.1286736</v>
+        <v>-1094.2912184</v>
       </c>
       <c r="O84">
-        <v>-376.29503576</v>
+        <v>-383.00192644</v>
       </c>
       <c r="P84">
-        <v>-698.8336378400002</v>
+        <v>-711.2892919600001</v>
       </c>
       <c r="Q84">
-        <v>-589.0336378400002</v>
+        <v>-601.4892919600002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2596070080027364</v>
+        <v>0.2721838908264269</v>
       </c>
       <c r="T84">
-        <v>3.111152482355725</v>
+        <v>3.294161451906063</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1105242989056596</v>
+        <v>0.1091926808465552</v>
       </c>
       <c r="W84">
-        <v>0.1786067207797435</v>
+        <v>0.1788741096860117</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3157837111590274</v>
+        <v>0.311979088133015</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1947367724798823</v>
+        <v>0.1962867724798823</v>
       </c>
       <c r="C85">
-        <v>-5151.346538145081</v>
+        <v>-5273.112616973388</v>
       </c>
       <c r="D85">
-        <v>2556.82646185492</v>
+        <v>2530.491383026613</v>
       </c>
       <c r="E85">
-        <v>6586.573</v>
+        <v>6682.004000000001</v>
       </c>
       <c r="F85">
-        <v>7920.773000000001</v>
+        <v>8016.204000000001</v>
       </c>
       <c r="G85">
         <v>212.6</v>
@@ -8257,37 +8257,37 @@
         <v>496.2</v>
       </c>
       <c r="M85">
-        <v>1590.4912184</v>
+        <v>1609.6537632</v>
       </c>
       <c r="N85">
-        <v>-1094.2912184</v>
+        <v>-1113.4537632</v>
       </c>
       <c r="O85">
-        <v>-383.00192644</v>
+        <v>-389.70881712</v>
       </c>
       <c r="P85">
-        <v>-711.2892919600001</v>
+        <v>-723.7449460800001</v>
       </c>
       <c r="Q85">
-        <v>-601.4892919600002</v>
+        <v>-613.9449460800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2721838908264269</v>
+        <v>0.2863328840030785</v>
       </c>
       <c r="T85">
-        <v>3.294161451906063</v>
+        <v>3.500046542650192</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1091926808465552</v>
+        <v>0.1078927679793343</v>
       </c>
       <c r="W85">
-        <v>0.1788741096860117</v>
+        <v>0.1791351321897497</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.311979088133015</v>
+        <v>0.3082650513695268</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1962867724798823</v>
+        <v>0.1978367724798822</v>
       </c>
       <c r="C86">
-        <v>-5273.112616973387</v>
+        <v>-5394.341728704615</v>
       </c>
       <c r="D86">
-        <v>2530.491383026613</v>
+        <v>2504.693271295385</v>
       </c>
       <c r="E86">
-        <v>6682.003999999999</v>
+        <v>6777.434999999999</v>
       </c>
       <c r="F86">
-        <v>8016.204</v>
+        <v>8111.635</v>
       </c>
       <c r="G86">
         <v>212.6</v>
@@ -8339,37 +8339,37 @@
         <v>496.2</v>
       </c>
       <c r="M86">
-        <v>1609.6537632</v>
+        <v>1628.816308</v>
       </c>
       <c r="N86">
-        <v>-1113.4537632</v>
+        <v>-1132.616308</v>
       </c>
       <c r="O86">
-        <v>-389.7088171199999</v>
+        <v>-396.4157078</v>
       </c>
       <c r="P86">
-        <v>-723.74494608</v>
+        <v>-736.2006002000001</v>
       </c>
       <c r="Q86">
-        <v>-613.94494608</v>
+        <v>-626.4006002000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2863328840030784</v>
+        <v>0.3023684096032836</v>
       </c>
       <c r="T86">
-        <v>3.500046542650189</v>
+        <v>3.733382978826869</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1078927679793344</v>
+        <v>0.1066234412972245</v>
       </c>
       <c r="W86">
-        <v>0.1791351321897497</v>
+        <v>0.1793900129875173</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3082650513695268</v>
+        <v>0.3046384037063559</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1978367724798822</v>
+        <v>0.1993867724798823</v>
       </c>
       <c r="C87">
-        <v>-5394.341728704615</v>
+        <v>-5515.050130578637</v>
       </c>
       <c r="D87">
-        <v>2504.693271295385</v>
+        <v>2479.415869421363</v>
       </c>
       <c r="E87">
-        <v>6777.434999999999</v>
+        <v>6872.866</v>
       </c>
       <c r="F87">
-        <v>8111.635</v>
+        <v>8207.066000000001</v>
       </c>
       <c r="G87">
         <v>212.6</v>
@@ -8421,37 +8421,37 @@
         <v>496.2</v>
       </c>
       <c r="M87">
-        <v>1628.816308</v>
+        <v>1647.9788528</v>
       </c>
       <c r="N87">
-        <v>-1132.616308</v>
+        <v>-1151.7788528</v>
       </c>
       <c r="O87">
-        <v>-396.4157078</v>
+        <v>-403.12259848</v>
       </c>
       <c r="P87">
-        <v>-736.2006002000001</v>
+        <v>-748.65625432</v>
       </c>
       <c r="Q87">
-        <v>-626.4006002000001</v>
+        <v>-638.8562543200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3023684096032836</v>
+        <v>0.3206947245749467</v>
       </c>
       <c r="T87">
-        <v>3.733382978826869</v>
+        <v>4.000053191600217</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1066234412972245</v>
+        <v>0.1053836338402801</v>
       </c>
       <c r="W87">
-        <v>0.1793900129875173</v>
+        <v>0.1796389663248718</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3046384037063559</v>
+        <v>0.3010960966865145</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1993867724798823</v>
+        <v>0.2009367724798823</v>
       </c>
       <c r="C88">
-        <v>-5515.050130578637</v>
+        <v>-5635.253430119039</v>
       </c>
       <c r="D88">
-        <v>2479.415869421363</v>
+        <v>2454.64356988096</v>
       </c>
       <c r="E88">
-        <v>6872.866</v>
+        <v>6968.296999999999</v>
       </c>
       <c r="F88">
-        <v>8207.066000000001</v>
+        <v>8302.496999999999</v>
       </c>
       <c r="G88">
         <v>212.6</v>
@@ -8503,37 +8503,37 @@
         <v>496.2</v>
       </c>
       <c r="M88">
-        <v>1647.9788528</v>
+        <v>1667.1413976</v>
       </c>
       <c r="N88">
-        <v>-1151.7788528</v>
+        <v>-1170.9413976</v>
       </c>
       <c r="O88">
-        <v>-403.12259848</v>
+        <v>-409.8294891599999</v>
       </c>
       <c r="P88">
-        <v>-748.65625432</v>
+        <v>-761.11190844</v>
       </c>
       <c r="Q88">
-        <v>-638.8562543200001</v>
+        <v>-651.31190844</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3206947245749467</v>
+        <v>0.3418404726191734</v>
       </c>
       <c r="T88">
-        <v>4.000053191600217</v>
+        <v>4.307749590954079</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1053836338402801</v>
+        <v>0.1041723277041849</v>
       </c>
       <c r="W88">
-        <v>0.1796389663248718</v>
+        <v>0.1798821965969997</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3010960966865145</v>
+        <v>0.2976352220119569</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2009367724798823</v>
+        <v>0.2024867724798823</v>
       </c>
       <c r="C89">
-        <v>-5635.253430119039</v>
+        <v>-5754.966617269229</v>
       </c>
       <c r="D89">
-        <v>2454.64356988096</v>
+        <v>2430.361382730771</v>
       </c>
       <c r="E89">
-        <v>6968.296999999999</v>
+        <v>7063.727999999999</v>
       </c>
       <c r="F89">
-        <v>8302.496999999999</v>
+        <v>8397.928</v>
       </c>
       <c r="G89">
         <v>212.6</v>
@@ -8585,37 +8585,37 @@
         <v>496.2</v>
       </c>
       <c r="M89">
-        <v>1667.1413976</v>
+        <v>1686.3039424</v>
       </c>
       <c r="N89">
-        <v>-1170.9413976</v>
+        <v>-1190.1039424</v>
       </c>
       <c r="O89">
-        <v>-409.8294891599999</v>
+        <v>-416.53637984</v>
       </c>
       <c r="P89">
-        <v>-761.11190844</v>
+        <v>-773.5675625600001</v>
       </c>
       <c r="Q89">
-        <v>-651.31190844</v>
+        <v>-663.7675625600001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3418404726191734</v>
+        <v>0.3665105120041046</v>
       </c>
       <c r="T89">
-        <v>4.307749590954079</v>
+        <v>4.666728723533587</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1041723277041849</v>
+        <v>0.102988551253001</v>
       </c>
       <c r="W89">
-        <v>0.1798821965969997</v>
+        <v>0.1801198989083974</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2976352220119569</v>
+        <v>0.2942530035800028</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2024867724798823</v>
+        <v>0.2040367724798823</v>
       </c>
       <c r="C90">
-        <v>-5754.966617269229</v>
+        <v>-5874.204094639788</v>
       </c>
       <c r="D90">
-        <v>2430.361382730771</v>
+        <v>2406.554905360213</v>
       </c>
       <c r="E90">
-        <v>7063.727999999999</v>
+        <v>7159.159</v>
       </c>
       <c r="F90">
-        <v>8397.928</v>
+        <v>8493.359</v>
       </c>
       <c r="G90">
         <v>212.6</v>
@@ -8667,37 +8667,37 @@
         <v>496.2</v>
       </c>
       <c r="M90">
-        <v>1686.3039424</v>
+        <v>1705.4664872</v>
       </c>
       <c r="N90">
-        <v>-1190.1039424</v>
+        <v>-1209.2664872</v>
       </c>
       <c r="O90">
-        <v>-416.53637984</v>
+        <v>-423.24327052</v>
       </c>
       <c r="P90">
-        <v>-773.5675625600001</v>
+        <v>-786.02321668</v>
       </c>
       <c r="Q90">
-        <v>-663.7675625600001</v>
+        <v>-676.2232166800001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3665105120041046</v>
+        <v>0.3956660130953867</v>
       </c>
       <c r="T90">
-        <v>4.666728723533587</v>
+        <v>5.090976789309367</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.102988551253001</v>
+        <v>0.1018313765198212</v>
       </c>
       <c r="W90">
-        <v>0.1801198989083974</v>
+        <v>0.1803522595948199</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2942530035800028</v>
+        <v>0.2909467900566319</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2040367724798823</v>
+        <v>0.2055867724798823</v>
       </c>
       <c r="C91">
-        <v>-5874.204094639788</v>
+        <v>-5992.979705995387</v>
       </c>
       <c r="D91">
-        <v>2406.554905360213</v>
+        <v>2383.210294004613</v>
       </c>
       <c r="E91">
-        <v>7159.159</v>
+        <v>7254.59</v>
       </c>
       <c r="F91">
-        <v>8493.359</v>
+        <v>8588.790000000001</v>
       </c>
       <c r="G91">
         <v>212.6</v>
@@ -8749,37 +8749,37 @@
         <v>496.2</v>
       </c>
       <c r="M91">
-        <v>1705.4664872</v>
+        <v>1724.629032</v>
       </c>
       <c r="N91">
-        <v>-1209.2664872</v>
+        <v>-1228.429032</v>
       </c>
       <c r="O91">
-        <v>-423.24327052</v>
+        <v>-429.9501612000001</v>
       </c>
       <c r="P91">
-        <v>-786.02321668</v>
+        <v>-798.4788708000001</v>
       </c>
       <c r="Q91">
-        <v>-676.2232166800001</v>
+        <v>-688.6788708000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3956660130953867</v>
+        <v>0.4306526144049255</v>
       </c>
       <c r="T91">
-        <v>5.090976789309367</v>
+        <v>5.600074468240305</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1018313765198212</v>
+        <v>0.1006999167807121</v>
       </c>
       <c r="W91">
-        <v>0.1803522595948199</v>
+        <v>0.180579456710433</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2909467900566319</v>
+        <v>0.2877140479448916</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2055867724798823</v>
+        <v>0.2071367724798823</v>
       </c>
       <c r="C92">
-        <v>-5992.979705995387</v>
+        <v>-6111.30676309959</v>
       </c>
       <c r="D92">
-        <v>2383.210294004613</v>
+        <v>2360.314236900411</v>
       </c>
       <c r="E92">
-        <v>7254.59</v>
+        <v>7350.021000000001</v>
       </c>
       <c r="F92">
-        <v>8588.790000000001</v>
+        <v>8684.221000000001</v>
       </c>
       <c r="G92">
         <v>212.6</v>
@@ -8831,37 +8831,37 @@
         <v>496.2</v>
       </c>
       <c r="M92">
-        <v>1724.629032</v>
+        <v>1743.7915768</v>
       </c>
       <c r="N92">
-        <v>-1228.429032</v>
+        <v>-1247.5915768</v>
       </c>
       <c r="O92">
-        <v>-429.9501612000001</v>
+        <v>-436.65705188</v>
       </c>
       <c r="P92">
-        <v>-798.4788708000001</v>
+        <v>-810.9345249200002</v>
       </c>
       <c r="Q92">
-        <v>-688.6788708000001</v>
+        <v>-701.1345249200002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4306526144049255</v>
+        <v>0.4734140160054728</v>
       </c>
       <c r="T92">
-        <v>5.600074468240305</v>
+        <v>6.22230496471145</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1006999167807121</v>
+        <v>0.09959332428861631</v>
       </c>
       <c r="W92">
-        <v>0.180579456710433</v>
+        <v>0.1808016604828458</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2877140479448916</v>
+        <v>0.2845523551103324</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2071367724798823</v>
+        <v>0.2086867724798823</v>
       </c>
       <c r="C93">
-        <v>-6111.30676309959</v>
+        <v>-6229.198071026973</v>
       </c>
       <c r="D93">
-        <v>2360.314236900411</v>
+        <v>2337.853928973028</v>
       </c>
       <c r="E93">
-        <v>7350.021000000001</v>
+        <v>7445.451999999999</v>
       </c>
       <c r="F93">
-        <v>8684.221000000001</v>
+        <v>8779.652</v>
       </c>
       <c r="G93">
         <v>212.6</v>
@@ -8913,37 +8913,37 @@
         <v>496.2</v>
       </c>
       <c r="M93">
-        <v>1743.7915768</v>
+        <v>1762.9541216</v>
       </c>
       <c r="N93">
-        <v>-1247.5915768</v>
+        <v>-1266.7541216</v>
       </c>
       <c r="O93">
-        <v>-436.65705188</v>
+        <v>-443.3639425599999</v>
       </c>
       <c r="P93">
-        <v>-810.9345249200002</v>
+        <v>-823.39017904</v>
       </c>
       <c r="Q93">
-        <v>-701.1345249200002</v>
+        <v>-713.5901790400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4734140160054728</v>
+        <v>0.526865768006157</v>
       </c>
       <c r="T93">
-        <v>6.22230496471145</v>
+        <v>7.000093085300383</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09959332428861631</v>
+        <v>0.09851078815504442</v>
       </c>
       <c r="W93">
-        <v>0.1808016604828458</v>
+        <v>0.1810190337384671</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2845523551103324</v>
+        <v>0.2814593947286983</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2086867724798823</v>
+        <v>0.2102367724798823</v>
       </c>
       <c r="C94">
-        <v>-6229.198071026973</v>
+        <v>-6346.665952043666</v>
       </c>
       <c r="D94">
-        <v>2337.853928973028</v>
+        <v>2315.817047956335</v>
       </c>
       <c r="E94">
-        <v>7445.451999999999</v>
+        <v>7540.883</v>
       </c>
       <c r="F94">
-        <v>8779.652</v>
+        <v>8875.083000000001</v>
       </c>
       <c r="G94">
         <v>212.6</v>
@@ -8995,37 +8995,37 @@
         <v>496.2</v>
       </c>
       <c r="M94">
-        <v>1762.9541216</v>
+        <v>1782.1166664</v>
       </c>
       <c r="N94">
-        <v>-1266.7541216</v>
+        <v>-1285.9166664</v>
       </c>
       <c r="O94">
-        <v>-443.3639425599999</v>
+        <v>-450.07083324</v>
       </c>
       <c r="P94">
-        <v>-823.39017904</v>
+        <v>-835.8458331600002</v>
       </c>
       <c r="Q94">
-        <v>-713.5901790400001</v>
+        <v>-726.0458331600003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.526865768006157</v>
+        <v>0.5955894491498938</v>
       </c>
       <c r="T94">
-        <v>7.000093085300383</v>
+        <v>8.000106383200439</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09851078815504442</v>
+        <v>0.09745153236843103</v>
       </c>
       <c r="W94">
-        <v>0.1810190337384671</v>
+        <v>0.1812317323004191</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2814593947286983</v>
+        <v>0.2784329496240886</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2102367724798823</v>
+        <v>0.2117867724798823</v>
       </c>
       <c r="C95">
-        <v>-6346.665952043666</v>
+        <v>-6463.722268149909</v>
       </c>
       <c r="D95">
-        <v>2315.817047956335</v>
+        <v>2294.191731850092</v>
       </c>
       <c r="E95">
-        <v>7540.883</v>
+        <v>7636.314</v>
       </c>
       <c r="F95">
-        <v>8875.083000000001</v>
+        <v>8970.514000000001</v>
       </c>
       <c r="G95">
         <v>212.6</v>
@@ -9077,37 +9077,37 @@
         <v>496.2</v>
       </c>
       <c r="M95">
-        <v>1782.1166664</v>
+        <v>1801.2792112</v>
       </c>
       <c r="N95">
-        <v>-1285.9166664</v>
+        <v>-1305.0792112</v>
       </c>
       <c r="O95">
-        <v>-450.07083324</v>
+        <v>-456.77772392</v>
       </c>
       <c r="P95">
-        <v>-835.8458331600002</v>
+        <v>-848.3014872800002</v>
       </c>
       <c r="Q95">
-        <v>-726.0458331600003</v>
+        <v>-738.5014872800002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5955894491498938</v>
+        <v>0.6872210240082096</v>
       </c>
       <c r="T95">
-        <v>8.000106383200439</v>
+        <v>9.333457447067181</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09745153236843103</v>
+        <v>0.09641481393897963</v>
       </c>
       <c r="W95">
-        <v>0.1812317323004191</v>
+        <v>0.1814399053610529</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2784329496240886</v>
+        <v>0.2754708969685132</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2117867724798823</v>
+        <v>0.2133367724798823</v>
       </c>
       <c r="C96">
-        <v>-6463.722268149909</v>
+        <v>-6580.378442371254</v>
       </c>
       <c r="D96">
-        <v>2294.191731850092</v>
+        <v>2272.966557628748</v>
       </c>
       <c r="E96">
-        <v>7636.314</v>
+        <v>7731.745000000001</v>
       </c>
       <c r="F96">
-        <v>8970.514000000001</v>
+        <v>9065.945000000002</v>
       </c>
       <c r="G96">
         <v>212.6</v>
@@ -9159,37 +9159,37 @@
         <v>496.2</v>
       </c>
       <c r="M96">
-        <v>1801.2792112</v>
+        <v>1820.441756</v>
       </c>
       <c r="N96">
-        <v>-1305.0792112</v>
+        <v>-1324.241756</v>
       </c>
       <c r="O96">
-        <v>-456.77772392</v>
+        <v>-463.4846146000001</v>
       </c>
       <c r="P96">
-        <v>-848.3014872800002</v>
+        <v>-860.7571414000003</v>
       </c>
       <c r="Q96">
-        <v>-738.5014872800002</v>
+        <v>-750.9571414000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6872210240082096</v>
+        <v>0.815505228809852</v>
       </c>
       <c r="T96">
-        <v>9.333457447067181</v>
+        <v>11.20014893648062</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09641481393897963</v>
+        <v>0.09539992116067456</v>
       </c>
       <c r="W96">
-        <v>0.1814399053610529</v>
+        <v>0.1816436958309366</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2754708969685132</v>
+        <v>0.2725712033162131</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2133367724798823</v>
+        <v>0.2148867724798822</v>
       </c>
       <c r="C97">
-        <v>-6580.378442371254</v>
+        <v>-6696.645478878745</v>
       </c>
       <c r="D97">
-        <v>2272.966557628748</v>
+        <v>2252.130521121256</v>
       </c>
       <c r="E97">
-        <v>7731.745000000001</v>
+        <v>7827.175999999999</v>
       </c>
       <c r="F97">
-        <v>9065.945000000002</v>
+        <v>9161.376</v>
       </c>
       <c r="G97">
         <v>212.6</v>
@@ -9241,37 +9241,37 @@
         <v>496.2</v>
       </c>
       <c r="M97">
-        <v>1820.441756</v>
+        <v>1839.6043008</v>
       </c>
       <c r="N97">
-        <v>-1324.241756</v>
+        <v>-1343.4043008</v>
       </c>
       <c r="O97">
-        <v>-463.4846146000001</v>
+        <v>-470.19150528</v>
       </c>
       <c r="P97">
-        <v>-860.7571414000003</v>
+        <v>-873.2127955200001</v>
       </c>
       <c r="Q97">
-        <v>-750.9571414000003</v>
+        <v>-763.4127955200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.815505228809852</v>
+        <v>1.007931536012315</v>
       </c>
       <c r="T97">
-        <v>11.20014893648062</v>
+        <v>14.00018617060078</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09539992116067456</v>
+        <v>0.09440617198191756</v>
       </c>
       <c r="W97">
-        <v>0.1816436958309366</v>
+        <v>0.1818432406660309</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2725712033162131</v>
+        <v>0.2697319199483359</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2148867724798822</v>
+        <v>0.2164367724798822</v>
       </c>
       <c r="C98">
-        <v>-6696.645478878745</v>
+        <v>-6812.533982012482</v>
       </c>
       <c r="D98">
-        <v>2252.130521121256</v>
+        <v>2231.673017987519</v>
       </c>
       <c r="E98">
-        <v>7827.175999999999</v>
+        <v>7922.607</v>
       </c>
       <c r="F98">
-        <v>9161.376</v>
+        <v>9256.807000000001</v>
       </c>
       <c r="G98">
         <v>212.6</v>
@@ -9323,37 +9323,37 @@
         <v>496.2</v>
       </c>
       <c r="M98">
-        <v>1839.6043008</v>
+        <v>1858.7668456</v>
       </c>
       <c r="N98">
-        <v>-1343.4043008</v>
+        <v>-1362.5668456</v>
       </c>
       <c r="O98">
-        <v>-470.19150528</v>
+        <v>-476.89839596</v>
       </c>
       <c r="P98">
-        <v>-873.2127955200001</v>
+        <v>-885.6684496400001</v>
       </c>
       <c r="Q98">
-        <v>-763.4127955200001</v>
+        <v>-775.8684496400001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.007931536012313</v>
+        <v>1.328642048016417</v>
       </c>
       <c r="T98">
-        <v>14.00018617060075</v>
+        <v>18.66691489413433</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09440617198191756</v>
+        <v>0.09343291247694933</v>
       </c>
       <c r="W98">
-        <v>0.1818432406660309</v>
+        <v>0.1820386711746286</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2697319199483359</v>
+        <v>0.2669511785055695</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2164367724798822</v>
+        <v>0.2179867724798823</v>
       </c>
       <c r="C99">
-        <v>-6812.533982012482</v>
+        <v>-6928.054174277729</v>
       </c>
       <c r="D99">
-        <v>2231.673017987519</v>
+        <v>2211.583825722271</v>
       </c>
       <c r="E99">
-        <v>7922.607</v>
+        <v>8018.037999999999</v>
       </c>
       <c r="F99">
-        <v>9256.807000000001</v>
+        <v>9352.237999999999</v>
       </c>
       <c r="G99">
         <v>212.6</v>
@@ -9405,37 +9405,37 @@
         <v>496.2</v>
       </c>
       <c r="M99">
-        <v>1858.7668456</v>
+        <v>1877.9293904</v>
       </c>
       <c r="N99">
-        <v>-1362.5668456</v>
+        <v>-1381.7293904</v>
       </c>
       <c r="O99">
-        <v>-476.89839596</v>
+        <v>-483.6052866399999</v>
       </c>
       <c r="P99">
-        <v>-885.6684496400001</v>
+        <v>-898.1241037599999</v>
       </c>
       <c r="Q99">
-        <v>-775.8684496400001</v>
+        <v>-788.32410376</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.328642048016417</v>
+        <v>1.970063072024626</v>
       </c>
       <c r="T99">
-        <v>18.66691489413433</v>
+        <v>28.0003723412015</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09343291247694933</v>
+        <v>0.09247951541085803</v>
       </c>
       <c r="W99">
-        <v>0.1820386711746286</v>
+        <v>0.1822301133054997</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2669511785055695</v>
+        <v>0.2642271868881658</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2179867724798823</v>
+        <v>0.2195367724798822</v>
       </c>
       <c r="C100">
-        <v>-6928.054174277729</v>
+        <v>-7043.215913377687</v>
       </c>
       <c r="D100">
-        <v>2211.583825722271</v>
+        <v>2191.853086622313</v>
       </c>
       <c r="E100">
-        <v>8018.037999999999</v>
+        <v>8113.468999999999</v>
       </c>
       <c r="F100">
-        <v>9352.237999999999</v>
+        <v>9447.669</v>
       </c>
       <c r="G100">
         <v>212.6</v>
@@ -9487,37 +9487,37 @@
         <v>496.2</v>
       </c>
       <c r="M100">
-        <v>1877.9293904</v>
+        <v>1897.0919352</v>
       </c>
       <c r="N100">
-        <v>-1381.7293904</v>
+        <v>-1400.8919352</v>
       </c>
       <c r="O100">
-        <v>-483.6052866399999</v>
+        <v>-490.31217732</v>
       </c>
       <c r="P100">
-        <v>-898.1241037599999</v>
+        <v>-910.57975788</v>
       </c>
       <c r="Q100">
-        <v>-788.32410376</v>
+        <v>-800.77975788</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.970063072024626</v>
+        <v>3.894326144049251</v>
       </c>
       <c r="T100">
-        <v>28.0003723412015</v>
+        <v>56.00074468240299</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09247951541085803</v>
+        <v>0.09154537889155642</v>
       </c>
       <c r="W100">
-        <v>0.1822301133054997</v>
+        <v>0.1824176879185755</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2642271868881658</v>
+        <v>0.261558225404447</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2195367724798822</v>
-      </c>
-      <c r="C101">
-        <v>-7043.215913377687</v>
-      </c>
-      <c r="D101">
-        <v>2191.853086622313</v>
-      </c>
-      <c r="E101">
-        <v>8113.468999999999</v>
-      </c>
-      <c r="F101">
-        <v>9447.669</v>
-      </c>
-      <c r="G101">
-        <v>212.6</v>
-      </c>
-      <c r="H101">
-        <v>8208.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>606</v>
-      </c>
-      <c r="K101">
-        <v>109.8</v>
-      </c>
-      <c r="L101">
-        <v>496.2</v>
-      </c>
-      <c r="M101">
-        <v>1897.0919352</v>
-      </c>
-      <c r="N101">
-        <v>-1400.8919352</v>
-      </c>
-      <c r="O101">
-        <v>-490.31217732</v>
-      </c>
-      <c r="P101">
-        <v>-910.57975788</v>
-      </c>
-      <c r="Q101">
-        <v>-800.77975788</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.894326144049251</v>
-      </c>
-      <c r="T101">
-        <v>56.00074468240299</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09154537889155642</v>
-      </c>
-      <c r="W101">
-        <v>0.1824176879185755</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.261558225404447</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
